--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -1171,10 +1171,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117816976</v>
+        <v>117816937</v>
       </c>
       <c r="B6" t="n">
-        <v>56933</v>
+        <v>57768</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1187,21 +1187,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102964</v>
+        <v>103018</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fiskmås</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Larus canus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1210,10 +1210,14 @@
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1258,7 +1262,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1268,7 +1272,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1295,10 +1299,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117816937</v>
+        <v>117816976</v>
       </c>
       <c r="B7" t="n">
-        <v>57768</v>
+        <v>56933</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1311,21 +1315,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103018</v>
+        <v>102964</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Fiskmås</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Larus canus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1334,14 +1338,10 @@
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>117711164</v>
       </c>
       <c r="B5" t="n">
-        <v>56751</v>
+        <v>56752</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1171,10 +1171,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117816937</v>
+        <v>117816976</v>
       </c>
       <c r="B6" t="n">
-        <v>57768</v>
+        <v>56934</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1187,21 +1187,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103018</v>
+        <v>102964</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Fiskmås</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Larus canus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1210,14 +1210,10 @@
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1262,7 +1258,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1272,7 +1268,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1299,10 +1295,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117816976</v>
+        <v>117816937</v>
       </c>
       <c r="B7" t="n">
-        <v>56933</v>
+        <v>57769</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1315,21 +1311,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102964</v>
+        <v>103018</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fiskmås</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Larus canus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1338,10 +1334,14 @@
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -1543,10 +1543,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118355065</v>
+        <v>118355322</v>
       </c>
       <c r="B9" t="n">
-        <v>57290</v>
+        <v>57724</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1559,45 +1559,49 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>102999</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>t, Jmt</t>
+          <t>45an, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525507</v>
+        <v>525458</v>
       </c>
       <c r="R9" t="n">
-        <v>7074702</v>
+        <v>7074700</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1663,10 +1667,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118355322</v>
+        <v>118355065</v>
       </c>
       <c r="B10" t="n">
-        <v>57724</v>
+        <v>57290</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1679,49 +1683,45 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102999</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>45an, Jmt</t>
+          <t>t, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>525458</v>
+        <v>525507</v>
       </c>
       <c r="R10" t="n">
-        <v>7074700</v>
+        <v>7074702</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>

--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -1543,10 +1543,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118355322</v>
+        <v>118355065</v>
       </c>
       <c r="B9" t="n">
-        <v>57724</v>
+        <v>57290</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1559,49 +1559,45 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102999</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>45an, Jmt</t>
+          <t>t, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525458</v>
+        <v>525507</v>
       </c>
       <c r="R9" t="n">
-        <v>7074700</v>
+        <v>7074702</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1667,10 +1663,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118355065</v>
+        <v>118355322</v>
       </c>
       <c r="B10" t="n">
-        <v>57290</v>
+        <v>57724</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1683,45 +1679,49 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>102999</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>t, Jmt</t>
+          <t>45an, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>525507</v>
+        <v>525458</v>
       </c>
       <c r="R10" t="n">
-        <v>7074702</v>
+        <v>7074700</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>

--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -2128,7 +2128,7 @@
         <v>121069884</v>
       </c>
       <c r="B14" t="n">
-        <v>56552</v>
+        <v>56555</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2243,6 +2243,126 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>121535633</v>
+      </c>
+      <c r="B15" t="n">
+        <v>55956</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>45an, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>525458</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7074700</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Stefan Prenker</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Stefan Prenker</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -2248,7 +2248,7 @@
         <v>121535633</v>
       </c>
       <c r="B15" t="n">
-        <v>55956</v>
+        <v>55957</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -2248,7 +2248,7 @@
         <v>121535633</v>
       </c>
       <c r="B15" t="n">
-        <v>55957</v>
+        <v>55958</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -2248,7 +2248,7 @@
         <v>121535633</v>
       </c>
       <c r="B15" t="n">
-        <v>55958</v>
+        <v>55959</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2363,6 +2363,130 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122944137</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>45an, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>525458</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7074700</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Stefan Prenker</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Stefan Prenker</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -2368,7 +2368,7 @@
         <v>122944137</v>
       </c>
       <c r="B16" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -2368,7 +2368,7 @@
         <v>122944137</v>
       </c>
       <c r="B16" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2487,6 +2487,224 @@
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>125990692</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57781</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>45an, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>525458</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7074700</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Stefan Prenker</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Stefan Prenker</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>125991602</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57524</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100096</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Fiskgjuse</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Pandion haliaetus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>45an, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>525458</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7074700</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Stefan Prenker</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Stefan Prenker</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -2492,7 +2492,7 @@
         <v>125990692</v>
       </c>
       <c r="B17" t="n">
-        <v>57781</v>
+        <v>57782</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>125991602</v>
       </c>
       <c r="B18" t="n">
-        <v>57524</v>
+        <v>57525</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -2492,7 +2492,7 @@
         <v>125990692</v>
       </c>
       <c r="B17" t="n">
-        <v>57782</v>
+        <v>57786</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>125991602</v>
       </c>
       <c r="B18" t="n">
-        <v>57525</v>
+        <v>57529</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -2492,7 +2492,7 @@
         <v>125990692</v>
       </c>
       <c r="B17" t="n">
-        <v>57786</v>
+        <v>57787</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>125991602</v>
       </c>
       <c r="B18" t="n">
-        <v>57529</v>
+        <v>57530</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -2819,7 +2819,7 @@
         <v>129090663</v>
       </c>
       <c r="B20" t="n">
-        <v>57850</v>
+        <v>57852</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -2819,7 +2819,7 @@
         <v>129090663</v>
       </c>
       <c r="B20" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2923,6 +2923,115 @@
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129540274</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57831</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>45an, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>525458</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7074700</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Stefan Prenker</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Stefan Prenker, Nora Dahlström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -2928,7 +2928,7 @@
         <v>129540274</v>
       </c>
       <c r="B21" t="n">
-        <v>57831</v>
+        <v>57834</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -2928,7 +2928,7 @@
         <v>129540274</v>
       </c>
       <c r="B21" t="n">
-        <v>57834</v>
+        <v>57839</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -2928,7 +2928,7 @@
         <v>129540274</v>
       </c>
       <c r="B21" t="n">
-        <v>57839</v>
+        <v>57840</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>116710205</v>
       </c>
       <c r="B2" t="n">
-        <v>57693</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58166</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -717,7 +712,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>

--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>116710205</v>
       </c>
       <c r="B2" t="n">
-        <v>58166</v>
+        <v>58168</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -2923,7 +2923,7 @@
         <v>129540274</v>
       </c>
       <c r="B21" t="n">
-        <v>57840</v>
+        <v>57841</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>116710205</v>
       </c>
       <c r="B2" t="n">
-        <v>58168</v>
+        <v>58171</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>116710205</v>
       </c>
       <c r="B2" t="n">
-        <v>58171</v>
+        <v>58172</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>116710205</v>
       </c>
       <c r="B2" t="n">
-        <v>58173</v>
+        <v>58258</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3027,6 +3027,111 @@
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>130845229</v>
+      </c>
+      <c r="B22" t="n">
+        <v>56436</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>avlägg, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>525477</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7074694</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Nora Dahlström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Nora Dahlström, Stefan Prenker</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>116710205</v>
+        <v>112943879</v>
       </c>
       <c r="B2" t="n">
-        <v>58173</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103001</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>45an, Jmt</t>
+          <t>vid stigen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>525458</v>
+        <v>525553</v>
       </c>
       <c r="R2" t="n">
-        <v>7074700</v>
+        <v>7074694</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -752,22 +752,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,65 +784,60 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>116790485</v>
+        <v>122944137</v>
       </c>
       <c r="B3" t="n">
-        <v>56743</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102961</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>pölen, Jmt</t>
+          <t>45an, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525444</v>
+        <v>525458</v>
       </c>
       <c r="R3" t="n">
-        <v>7074699</v>
+        <v>7074700</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,22 +861,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,27 +891,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117156792</v>
+        <v>111388908</v>
       </c>
       <c r="B4" t="n">
-        <v>56746</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58067</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,21 +914,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102961</v>
+        <v>100090</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Nucifraga caryocatactes</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -960,20 +940,20 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>45an, Jmt</t>
+          <t>vid stigen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525458</v>
+        <v>525553</v>
       </c>
       <c r="R4" t="n">
-        <v>7074700</v>
+        <v>7074694</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1000,22 +980,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2023-08-10</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2023-08-10</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1042,37 +1022,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117711164</v>
+        <v>125991602</v>
       </c>
       <c r="B5" t="n">
-        <v>56754</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57825</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102961</v>
+        <v>100096</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1084,23 +1059,23 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>avlägg, Jmt</t>
+          <t>45an, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525477</v>
+        <v>525458</v>
       </c>
       <c r="R5" t="n">
-        <v>7074694</v>
+        <v>7074700</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1124,22 +1099,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,27 +1119,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117816976</v>
+        <v>118166153</v>
       </c>
       <c r="B6" t="n">
-        <v>56936</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1182,49 +1142,45 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102964</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fiskmås</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Larus canus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>45an, Jmt</t>
+          <t>t, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>525458</v>
+        <v>525477</v>
       </c>
       <c r="R6" t="n">
-        <v>7074700</v>
+        <v>7074713</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1248,22 +1204,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1290,15 +1246,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117816937</v>
+        <v>118166213</v>
       </c>
       <c r="B7" t="n">
-        <v>57771</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1306,53 +1257,45 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103018</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>45an, Jmt</t>
+          <t>t, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>525458</v>
+        <v>525499</v>
       </c>
       <c r="R7" t="n">
-        <v>7074700</v>
+        <v>7074704</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1376,22 +1319,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1418,15 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118166213</v>
+        <v>118355065</v>
       </c>
       <c r="B8" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,10 +1404,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>525499</v>
+        <v>525507</v>
       </c>
       <c r="R8" t="n">
-        <v>7074704</v>
+        <v>7074702</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1496,7 +1434,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -1506,7 +1444,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1538,15 +1476,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118355065</v>
+        <v>118355195</v>
       </c>
       <c r="B9" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1586,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525507</v>
+        <v>525516</v>
       </c>
       <c r="R9" t="n">
-        <v>7074702</v>
+        <v>7074704</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1658,15 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118355322</v>
+        <v>118635758</v>
       </c>
       <c r="B10" t="n">
-        <v>57724</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,49 +1602,45 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102999</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>45an, Jmt</t>
+          <t>avlägg, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>525458</v>
+        <v>525477</v>
       </c>
       <c r="R10" t="n">
-        <v>7074700</v>
+        <v>7074694</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1740,22 +1664,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1770,27 +1684,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118635758</v>
+        <v>119317623</v>
       </c>
       <c r="B11" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1826,17 +1735,17 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>avlägg, Jmt</t>
+          <t>vid stigen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>525477</v>
+        <v>525553</v>
       </c>
       <c r="R11" t="n">
         <v>7074694</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1860,12 +1769,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1880,27 +1799,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119104405</v>
+        <v>125605376</v>
       </c>
       <c r="B12" t="n">
-        <v>57461</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,49 +1822,49 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>45an, Jmt</t>
+          <t>bnm, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>525458</v>
+        <v>525550</v>
       </c>
       <c r="R12" t="n">
-        <v>7074700</v>
+        <v>7074647</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1974,12 +1888,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1994,77 +1918,68 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström, Stefan Prenker</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119389819</v>
+        <v>107420832</v>
       </c>
       <c r="B13" t="n">
-        <v>57463</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>avlägg, Jmt</t>
+          <t>vid stigen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>525477</v>
+        <v>525553</v>
       </c>
       <c r="R13" t="n">
         <v>7074694</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2088,12 +2003,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2023-03-20</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2023-03-20</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2108,44 +2033,39 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121069884</v>
+        <v>112943997</v>
       </c>
       <c r="B14" t="n">
-        <v>56555</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58592</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>102125</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2153,28 +2073,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>avlägg, Jmt</t>
+          <t>vid stigen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>525477</v>
+        <v>525553</v>
       </c>
       <c r="R14" t="n">
         <v>7074694</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2198,22 +2122,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:40</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:40</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2228,52 +2142,51 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121535633</v>
+        <v>115140075</v>
       </c>
       <c r="B15" t="n">
-        <v>55959</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>206004</v>
+        <v>102612</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
@@ -2284,14 +2197,14 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>45an, Jmt</t>
+          <t>vid stigen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>525458</v>
+        <v>525553</v>
       </c>
       <c r="R15" t="n">
-        <v>7074700</v>
+        <v>7074694</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2318,22 +2231,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2360,32 +2263,27 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122944137</v>
+        <v>121069884</v>
       </c>
       <c r="B16" t="n">
-        <v>57503</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2393,32 +2291,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>45an, Jmt</t>
+          <t>avlägg, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>525458</v>
+        <v>525477</v>
       </c>
       <c r="R16" t="n">
-        <v>7074700</v>
+        <v>7074694</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2442,22 +2336,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2472,69 +2366,69 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125990692</v>
+        <v>111991462</v>
       </c>
       <c r="B17" t="n">
-        <v>57787</v>
+        <v>57144</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>205976</v>
+        <v>102613</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>45an, Jmt</t>
+          <t>vid stigen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>525458</v>
+        <v>525553</v>
       </c>
       <c r="R17" t="n">
-        <v>7074700</v>
+        <v>7074694</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2561,12 +2455,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2593,60 +2497,60 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125991602</v>
+        <v>116790485</v>
       </c>
       <c r="B18" t="n">
-        <v>57530</v>
+        <v>57369</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100096</v>
+        <v>102961</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pandion haliaetus</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>45an, Jmt</t>
+          <t>pölen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>525458</v>
+        <v>525444</v>
       </c>
       <c r="R18" t="n">
-        <v>7074700</v>
+        <v>7074699</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2670,12 +2574,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2690,22 +2604,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126659326</v>
+        <v>117156792</v>
       </c>
       <c r="B19" t="n">
-        <v>57987</v>
+        <v>57369</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2713,21 +2627,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103008</v>
+        <v>102961</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2739,7 +2653,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2779,12 +2693,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2804,17 +2728,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Stefan Prenker, Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129090663</v>
+        <v>117711164</v>
       </c>
       <c r="B20" t="n">
-        <v>57854</v>
+        <v>57369</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2822,16 +2746,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103035</v>
+        <v>102961</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2841,14 +2765,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2888,12 +2812,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2920,44 +2854,44 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129540274</v>
+        <v>116710218</v>
       </c>
       <c r="B21" t="n">
-        <v>57841</v>
+        <v>58541</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103031</v>
+        <v>102987</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2997,12 +2931,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2024-05-08</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2024-05-08</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3022,17 +2966,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Stefan Prenker, Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130845229</v>
+        <v>119607835</v>
       </c>
       <c r="B22" t="n">
-        <v>56456</v>
+        <v>58541</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,16 +2984,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>206004</v>
+        <v>102987</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3057,12 +3001,16 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3102,12 +3050,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3127,51 +3075,51 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Nora Dahlström, Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132177647</v>
+        <v>118355322</v>
       </c>
       <c r="B23" t="n">
-        <v>58603</v>
+        <v>58393</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103042</v>
+        <v>102999</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3211,7 +3159,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
@@ -3221,7 +3169,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -3246,51 +3194,51 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Stefan Prenker, Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134208274</v>
+        <v>116710205</v>
       </c>
       <c r="B24" t="n">
-        <v>58349</v>
+        <v>58388</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>103001</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3330,12 +3278,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2024-05-08</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2024-05-08</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3355,10 +3313,2160 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
+          <t>Stefan Prenker</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>126659326</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58286</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103008</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ärtsångare</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Curruca curruca</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>45an, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>525458</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7074700</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Stefan Prenker</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
           <t>Stefan Prenker, Nora Dahlström</t>
         </is>
       </c>
-      <c r="AY24" t="inlineStr"/>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>134208274</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58349</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>45an, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>525458</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7074700</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Stefan Prenker</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Stefan Prenker, Nora Dahlström</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>134456500</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58349</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>vid stigen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>525553</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7074694</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Stefan Prenker</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Stefan Prenker, Nora Dahlström</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>117816937</v>
+      </c>
+      <c r="B28" t="n">
+        <v>58439</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>45an, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>525458</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7074700</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-06-16</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-06-16</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Stefan Prenker</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Stefan Prenker</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>110849212</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>vid stigen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>525553</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7074694</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2023-07-15</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2023-07-15</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Stefan Prenker</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Stefan Prenker</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>119104405</v>
+      </c>
+      <c r="B30" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>45an, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>525458</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7074700</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Stefan Prenker</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Stefan Prenker</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>119389819</v>
+      </c>
+      <c r="B31" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>avlägg, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>525477</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7074694</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Nora Dahlström</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Nora Dahlström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129090796</v>
+      </c>
+      <c r="B32" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>bnm, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>525550</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7074647</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Nora Dahlström</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Nora Dahlström</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>115275704</v>
+      </c>
+      <c r="B33" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>vid stigen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>525553</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7074694</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-03-19</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-03-19</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Stefan Prenker</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Stefan Prenker</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129540274</v>
+      </c>
+      <c r="B34" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>45an, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>525458</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7074700</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Stefan Prenker</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Stefan Prenker, Nora Dahlström</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129090663</v>
+      </c>
+      <c r="B35" t="n">
+        <v>58082</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>103035</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Kråka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Corvus corone</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>avlägg, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>525477</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7074694</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Nora Dahlström</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Nora Dahlström</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>132177647</v>
+      </c>
+      <c r="B36" t="n">
+        <v>58624</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>45an, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>525458</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7074700</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Stefan Prenker</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Stefan Prenker, Nora Dahlström</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>133167590</v>
+      </c>
+      <c r="B37" t="n">
+        <v>58658</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>vid stigen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>525553</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7074694</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Stefan Prenker</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Stefan Prenker, Nora Dahlström</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128105819</v>
+      </c>
+      <c r="B38" t="n">
+        <v>43258</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>201129</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vitfläckig guldvinge</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Lycaena virgaureae</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>avlägg, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>525477</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7074694</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Nora Dahlström</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Nora Dahlström, Stefan Prenker</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>114532044</v>
+      </c>
+      <c r="B39" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>vid stigen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>525553</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7074694</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-02-04</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-02-04</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Stefan Prenker</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Stefan Prenker</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>117243737</v>
+      </c>
+      <c r="B40" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>pölen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>525444</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7074699</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Nora Dahlström</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Nora Dahlström</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>118197285</v>
+      </c>
+      <c r="B41" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>45an, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>525458</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7074700</v>
+      </c>
+      <c r="S41" t="n">
+        <v>25</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Stefan Prenker</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Stefan Prenker</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>121535633</v>
+      </c>
+      <c r="B42" t="n">
+        <v>56522</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>45an, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>525458</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7074700</v>
+      </c>
+      <c r="S42" t="n">
+        <v>25</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Stefan Prenker</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Stefan Prenker</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>130845229</v>
+      </c>
+      <c r="B43" t="n">
+        <v>56522</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>avlägg, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>525477</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7074694</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Nora Dahlström</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Nora Dahlström, Stefan Prenker</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5468,6 +5468,112 @@
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>134600253</v>
+      </c>
+      <c r="B44" t="n">
+        <v>108205</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>brudborste, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>525446</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7074703</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Nora Dahlström</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Nora Dahlström, Stefan Prenker</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AY49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -903,27 +903,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111388908</v>
+        <v>135234736</v>
       </c>
       <c r="B4" t="n">
-        <v>58067</v>
+        <v>57280</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100090</v>
+        <v>100065</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nucifraga caryocatactes</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -946,14 +946,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>vid stigen, Jmt</t>
+          <t>45an, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525553</v>
+        <v>525458</v>
       </c>
       <c r="R4" t="n">
-        <v>7074694</v>
+        <v>7074700</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -980,22 +980,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-08-10</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-08-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,27 +1012,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125991602</v>
+        <v>111388908</v>
       </c>
       <c r="B5" t="n">
-        <v>57825</v>
+        <v>58067</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100096</v>
+        <v>100090</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pandion haliaetus</t>
+          <t>Nucifraga caryocatactes</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1059,20 +1049,20 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>45an, Jmt</t>
+          <t>vid stigen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525458</v>
+        <v>525553</v>
       </c>
       <c r="R5" t="n">
-        <v>7074700</v>
+        <v>7074694</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1099,12 +1089,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2023-08-10</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2023-08-10</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,27 +1131,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118166153</v>
+        <v>125991602</v>
       </c>
       <c r="B6" t="n">
-        <v>57953</v>
+        <v>57825</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100096</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1159,28 +1159,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>t, Jmt</t>
+          <t>45an, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>525477</v>
+        <v>525458</v>
       </c>
       <c r="R6" t="n">
-        <v>7074713</v>
+        <v>7074700</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1204,22 +1208,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,7 +1240,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118166213</v>
+        <v>118166153</v>
       </c>
       <c r="B7" t="n">
         <v>57953</v>
@@ -1289,10 +1283,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>525499</v>
+        <v>525477</v>
       </c>
       <c r="R7" t="n">
-        <v>7074704</v>
+        <v>7074713</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1361,7 +1355,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118355065</v>
+        <v>118166213</v>
       </c>
       <c r="B8" t="n">
         <v>57953</v>
@@ -1404,10 +1398,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>525507</v>
+        <v>525499</v>
       </c>
       <c r="R8" t="n">
-        <v>7074702</v>
+        <v>7074704</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1434,7 +1428,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -1444,7 +1438,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1476,7 +1470,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118355195</v>
+        <v>118355065</v>
       </c>
       <c r="B9" t="n">
         <v>57953</v>
@@ -1519,10 +1513,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525516</v>
+        <v>525507</v>
       </c>
       <c r="R9" t="n">
-        <v>7074704</v>
+        <v>7074702</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1591,7 +1585,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118635758</v>
+        <v>118355195</v>
       </c>
       <c r="B10" t="n">
         <v>57953</v>
@@ -1630,17 +1624,17 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>avlägg, Jmt</t>
+          <t>t, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>525477</v>
+        <v>525516</v>
       </c>
       <c r="R10" t="n">
-        <v>7074694</v>
+        <v>7074704</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1664,12 +1658,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-10</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-10</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1684,19 +1688,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119317623</v>
+        <v>118635758</v>
       </c>
       <c r="B11" t="n">
         <v>57953</v>
@@ -1735,17 +1739,17 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>vid stigen, Jmt</t>
+          <t>avlägg, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>525553</v>
+        <v>525477</v>
       </c>
       <c r="R11" t="n">
         <v>7074694</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1769,22 +1773,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1799,19 +1793,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125605376</v>
+        <v>119317623</v>
       </c>
       <c r="B12" t="n">
         <v>57953</v>
@@ -1839,32 +1833,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>bnm, Jmt</t>
+          <t>vid stigen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>525550</v>
+        <v>525553</v>
       </c>
       <c r="R12" t="n">
-        <v>7074647</v>
+        <v>7074694</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1888,22 +1878,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1918,68 +1908,72 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Nora Dahlström, Stefan Prenker</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>107420832</v>
+        <v>125605376</v>
       </c>
       <c r="B13" t="n">
-        <v>57141</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>vid stigen, Jmt</t>
+          <t>bnm, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>525553</v>
+        <v>525550</v>
       </c>
       <c r="R13" t="n">
-        <v>7074694</v>
+        <v>7074647</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2003,22 +1997,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-03-20</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-03-20</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2033,22 +2027,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström, Stefan Prenker</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112943997</v>
+        <v>107420832</v>
       </c>
       <c r="B14" t="n">
-        <v>58592</v>
+        <v>57141</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2056,33 +2050,29 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102125</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2122,12 +2112,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-03-20</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-03-20</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2154,10 +2154,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>115140075</v>
+        <v>112943997</v>
       </c>
       <c r="B15" t="n">
-        <v>57132</v>
+        <v>58592</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2165,16 +2165,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102612</v>
+        <v>102125</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2184,14 +2184,14 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2231,12 +2231,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2263,7 +2263,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121069884</v>
+        <v>115140075</v>
       </c>
       <c r="B16" t="n">
         <v>57132</v>
@@ -2291,7 +2291,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
@@ -2302,17 +2306,17 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>avlägg, Jmt</t>
+          <t>vid stigen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>525477</v>
+        <v>525553</v>
       </c>
       <c r="R16" t="n">
         <v>7074694</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2336,22 +2340,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>13:40</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:40</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2366,22 +2360,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>111991462</v>
+        <v>121069884</v>
       </c>
       <c r="B17" t="n">
-        <v>57144</v>
+        <v>57132</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2389,16 +2383,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102613</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2406,32 +2400,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>vid stigen, Jmt</t>
+          <t>avlägg, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>525553</v>
+        <v>525477</v>
       </c>
       <c r="R17" t="n">
         <v>7074694</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2455,22 +2445,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2485,44 +2475,44 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>116790485</v>
+        <v>111991462</v>
       </c>
       <c r="B18" t="n">
-        <v>57369</v>
+        <v>57144</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102961</v>
+        <v>102613</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2534,23 +2524,23 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>pölen, Jmt</t>
+          <t>vid stigen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>525444</v>
+        <v>525553</v>
       </c>
       <c r="R18" t="n">
-        <v>7074699</v>
+        <v>7074694</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2574,22 +2564,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2604,19 +2594,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117156792</v>
+        <v>116790485</v>
       </c>
       <c r="B19" t="n">
         <v>57369</v>
@@ -2646,7 +2636,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -2659,17 +2649,17 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>45an, Jmt</t>
+          <t>pölen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>525458</v>
+        <v>525444</v>
       </c>
       <c r="R19" t="n">
-        <v>7074700</v>
+        <v>7074699</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2693,17 +2683,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -2723,19 +2713,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117711164</v>
+        <v>117156792</v>
       </c>
       <c r="B20" t="n">
         <v>57369</v>
@@ -2772,23 +2762,23 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>avlägg, Jmt</t>
+          <t>45an, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>525477</v>
+        <v>525458</v>
       </c>
       <c r="R20" t="n">
-        <v>7074694</v>
+        <v>7074700</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2812,22 +2802,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2842,22 +2832,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>116710218</v>
+        <v>117711164</v>
       </c>
       <c r="B21" t="n">
-        <v>58541</v>
+        <v>57369</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2865,16 +2855,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102987</v>
+        <v>102961</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sädesärla</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Motacilla alba</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2891,23 +2881,23 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>45an, Jmt</t>
+          <t>avlägg, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>525458</v>
+        <v>525477</v>
       </c>
       <c r="R21" t="n">
-        <v>7074700</v>
+        <v>7074694</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2931,22 +2921,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2961,19 +2951,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119607835</v>
+        <v>116710218</v>
       </c>
       <c r="B22" t="n">
         <v>58541</v>
@@ -3016,17 +3006,17 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>avlägg, Jmt</t>
+          <t>45an, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>525477</v>
+        <v>525458</v>
       </c>
       <c r="R22" t="n">
-        <v>7074694</v>
+        <v>7074700</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3050,12 +3040,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-05-08</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-05-08</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3070,22 +3070,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118355322</v>
+        <v>119607835</v>
       </c>
       <c r="B23" t="n">
-        <v>58393</v>
+        <v>58541</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3093,16 +3093,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102999</v>
+        <v>102987</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3112,30 +3112,30 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>45an, Jmt</t>
+          <t>avlägg, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>525458</v>
+        <v>525477</v>
       </c>
       <c r="R23" t="n">
-        <v>7074700</v>
+        <v>7074694</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3159,22 +3159,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3189,22 +3179,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>116710205</v>
+        <v>118355322</v>
       </c>
       <c r="B24" t="n">
-        <v>58388</v>
+        <v>58393</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3212,33 +3202,33 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103001</v>
+        <v>102999</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3278,22 +3268,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3320,44 +3310,44 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126659326</v>
+        <v>116710205</v>
       </c>
       <c r="B25" t="n">
-        <v>58286</v>
+        <v>58388</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103008</v>
+        <v>103001</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3397,12 +3387,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2024-05-08</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2024-05-08</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Stefan Prenker, Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134208274</v>
+        <v>126659326</v>
       </c>
       <c r="B26" t="n">
-        <v>58349</v>
+        <v>58286</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3440,16 +3440,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>103008</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3466,7 +3466,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3506,12 +3506,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2025-07-13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2025-07-13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3538,7 +3538,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134456500</v>
+        <v>134208274</v>
       </c>
       <c r="B27" t="n">
         <v>58349</v>
@@ -3575,20 +3575,20 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>vid stigen, Jmt</t>
+          <t>45an, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>525553</v>
+        <v>525458</v>
       </c>
       <c r="R27" t="n">
-        <v>7074694</v>
+        <v>7074700</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3615,22 +3615,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3657,10 +3647,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117816937</v>
+        <v>134456500</v>
       </c>
       <c r="B28" t="n">
-        <v>58439</v>
+        <v>58349</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3668,21 +3658,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3691,27 +3681,23 @@
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>45an, Jmt</t>
+          <t>vid stigen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>525458</v>
+        <v>525553</v>
       </c>
       <c r="R28" t="n">
-        <v>7074700</v>
+        <v>7074694</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3738,22 +3724,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3773,39 +3759,39 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Stefan Prenker, Nora Dahlström</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>110849212</v>
+        <v>117816937</v>
       </c>
       <c r="B29" t="n">
-        <v>58114</v>
+        <v>58439</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>103018</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3814,23 +3800,27 @@
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>vid stigen, Jmt</t>
+          <t>45an, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>525553</v>
+        <v>525458</v>
       </c>
       <c r="R29" t="n">
-        <v>7074694</v>
+        <v>7074700</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3857,22 +3847,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2023-07-15</t>
+          <t>2024-06-16</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2023-07-15</t>
+          <t>2024-06-16</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3899,7 +3889,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119104405</v>
+        <v>110849212</v>
       </c>
       <c r="B30" t="n">
         <v>58114</v>
@@ -3929,27 +3919,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>45an, Jmt</t>
+          <t>vid stigen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>525458</v>
+        <v>525553</v>
       </c>
       <c r="R30" t="n">
-        <v>7074700</v>
+        <v>7074694</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3976,12 +3966,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2023-07-15</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2023-07-15</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4008,7 +4008,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119389819</v>
+        <v>119104405</v>
       </c>
       <c r="B31" t="n">
         <v>58114</v>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -4051,17 +4051,17 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>avlägg, Jmt</t>
+          <t>45an, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>525477</v>
+        <v>525458</v>
       </c>
       <c r="R31" t="n">
-        <v>7074694</v>
+        <v>7074700</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4085,12 +4085,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4105,19 +4105,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129090796</v>
+        <v>119389819</v>
       </c>
       <c r="B32" t="n">
         <v>58114</v>
@@ -4145,25 +4145,29 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>bnm, Jmt</t>
+          <t>avlägg, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>525550</v>
+        <v>525477</v>
       </c>
       <c r="R32" t="n">
-        <v>7074647</v>
+        <v>7074694</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4190,12 +4194,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4222,10 +4226,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>115275704</v>
+        <v>129090796</v>
       </c>
       <c r="B33" t="n">
-        <v>58057</v>
+        <v>58114</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4233,49 +4237,45 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>vid stigen, Jmt</t>
+          <t>bnm, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>525553</v>
+        <v>525550</v>
       </c>
       <c r="R33" t="n">
-        <v>7074694</v>
+        <v>7074647</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4299,22 +4299,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4329,22 +4319,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129540274</v>
+        <v>135235591</v>
       </c>
       <c r="B34" t="n">
-        <v>58057</v>
+        <v>58136</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4352,49 +4342,49 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>45an, Jmt</t>
+          <t>kj, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>525458</v>
+        <v>525528</v>
       </c>
       <c r="R34" t="n">
-        <v>7074700</v>
+        <v>7074639</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4418,12 +4408,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4438,44 +4428,44 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Stefan Prenker, Nora Dahlström</t>
+          <t>Nora Dahlström, Stefan Prenker</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129090663</v>
+        <v>115275704</v>
       </c>
       <c r="B35" t="n">
-        <v>58082</v>
+        <v>58057</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103035</v>
+        <v>103031</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4487,23 +4477,23 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>avlägg, Jmt</t>
+          <t>vid stigen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>525477</v>
+        <v>525553</v>
       </c>
       <c r="R35" t="n">
         <v>7074694</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4527,12 +4517,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2024-03-19</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2024-03-19</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4547,39 +4547,39 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132177647</v>
+        <v>129540274</v>
       </c>
       <c r="B36" t="n">
-        <v>58624</v>
+        <v>58057</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103042</v>
+        <v>103031</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4589,14 +4589,14 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4636,22 +4636,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4678,10 +4668,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133167590</v>
+        <v>129090663</v>
       </c>
       <c r="B37" t="n">
-        <v>58658</v>
+        <v>58082</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4689,49 +4679,49 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103044</v>
+        <v>103035</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Corvus corone</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>vid stigen, Jmt</t>
+          <t>avlägg, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>525553</v>
+        <v>525477</v>
       </c>
       <c r="R37" t="n">
         <v>7074694</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4755,22 +4745,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4785,39 +4765,39 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Stefan Prenker, Nora Dahlström</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128105819</v>
+        <v>132177647</v>
       </c>
       <c r="B38" t="n">
-        <v>43258</v>
+        <v>58624</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>201129</v>
+        <v>103042</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitfläckig guldvinge</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycaena virgaureae</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4830,24 +4810,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>avlägg, Jmt</t>
+          <t>45an, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>525477</v>
+        <v>525458</v>
       </c>
       <c r="R38" t="n">
-        <v>7074694</v>
+        <v>7074700</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4871,12 +4854,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4885,76 +4878,78 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Nora Dahlström, Stefan Prenker</t>
+          <t>Stefan Prenker, Nora Dahlström</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135071522</v>
+        <v>133167590</v>
       </c>
       <c r="B39" t="n">
-        <v>43314</v>
+        <v>58658</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>201146</v>
+        <v>103044</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Silverblåvinge</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Polyommatus amandus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schneider, 1792)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>avlägg, Jmt</t>
+          <t>vid stigen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>525477</v>
+        <v>525553</v>
       </c>
       <c r="R39" t="n">
         <v>7074694</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4978,12 +4973,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4992,79 +4997,75 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Nora Dahlström, Stefan Prenker</t>
+          <t>Stefan Prenker, Nora Dahlström</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>114532044</v>
+        <v>128105819</v>
       </c>
       <c r="B40" t="n">
-        <v>58085</v>
+        <v>43258</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>205976</v>
+        <v>201129</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Vitfläckig guldvinge</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Lycaena virgaureae</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>vid stigen, Jmt</t>
+          <t>avlägg, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>525553</v>
+        <v>525477</v>
       </c>
       <c r="R40" t="n">
         <v>7074694</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5088,12 +5089,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5102,50 +5103,51 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström, Stefan Prenker</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117243737</v>
+        <v>135071522</v>
       </c>
       <c r="B41" t="n">
-        <v>58085</v>
+        <v>43314</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>205976</v>
+        <v>201146</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Silverblåvinge</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Polyommatus amandus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schneider, 1792)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5153,24 +5155,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>pölen, Jmt</t>
+          <t>avlägg, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>525444</v>
+        <v>525477</v>
       </c>
       <c r="R41" t="n">
-        <v>7074699</v>
+        <v>7074694</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5197,22 +5196,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5221,6 +5210,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5232,14 +5222,14 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Nora Dahlström, Stefan Prenker</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118197285</v>
+        <v>114532044</v>
       </c>
       <c r="B42" t="n">
         <v>58085</v>
@@ -5269,9 +5259,10 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
@@ -5281,14 +5272,14 @@
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>45an, Jmt</t>
+          <t>vid stigen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>525458</v>
+        <v>525553</v>
       </c>
       <c r="R42" t="n">
-        <v>7074700</v>
+        <v>7074694</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5315,22 +5306,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5357,27 +5338,27 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121535633</v>
+        <v>117243737</v>
       </c>
       <c r="B43" t="n">
-        <v>56522</v>
+        <v>58085</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>206004</v>
+        <v>205976</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5385,28 +5366,32 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>45an, Jmt</t>
+          <t>pölen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>525458</v>
+        <v>525444</v>
       </c>
       <c r="R43" t="n">
-        <v>7074700</v>
+        <v>7074699</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5430,7 +5415,7 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
@@ -5440,12 +5425,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5460,39 +5445,39 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130845229</v>
+        <v>118197285</v>
       </c>
       <c r="B44" t="n">
-        <v>56522</v>
+        <v>58085</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>206004</v>
+        <v>205976</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5500,28 +5485,31 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>avlägg, Jmt</t>
+          <t>45an, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>525477</v>
+        <v>525458</v>
       </c>
       <c r="R44" t="n">
-        <v>7074694</v>
+        <v>7074700</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5545,12 +5533,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5565,39 +5563,39 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Nora Dahlström, Stefan Prenker</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135071023</v>
+        <v>121535633</v>
       </c>
       <c r="B45" t="n">
-        <v>58839</v>
+        <v>56522</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>208249</v>
+        <v>206004</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5605,29 +5603,28 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>avlägg, Jmt</t>
+          <t>45an, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>525477</v>
+        <v>525458</v>
       </c>
       <c r="R45" t="n">
-        <v>7074694</v>
+        <v>7074700</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5651,12 +5648,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5665,72 +5672,71 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Nora Dahlström, Stefan Prenker</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134600253</v>
+        <v>130845229</v>
       </c>
       <c r="B46" t="n">
-        <v>108205</v>
+        <v>56522</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220083</v>
+        <v>206004</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>brudborste, Jmt</t>
+          <t>avlägg, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>525446</v>
+        <v>525477</v>
       </c>
       <c r="R46" t="n">
-        <v>7074703</v>
+        <v>7074694</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5757,12 +5763,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5771,7 +5777,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5787,6 +5792,330 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135071023</v>
+      </c>
+      <c r="B47" t="n">
+        <v>58839</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>avlägg, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>525477</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7074694</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Nora Dahlström</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Nora Dahlström, Stefan Prenker</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135234743</v>
+      </c>
+      <c r="B48" t="n">
+        <v>58839</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>45an, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>525458</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7074700</v>
+      </c>
+      <c r="S48" t="n">
+        <v>25</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Stefan Prenker</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Stefan Prenker</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>134600253</v>
+      </c>
+      <c r="B49" t="n">
+        <v>108205</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>brudborste, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>525446</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7074703</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Nora Dahlström</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Nora Dahlström, Stefan Prenker</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY49"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5229,60 +5229,61 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>114532044</v>
+        <v>135545845</v>
       </c>
       <c r="B42" t="n">
-        <v>58085</v>
+        <v>43314</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>205976</v>
+        <v>201146</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Silverblåvinge</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Polyommatus amandus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schneider, 1792)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>vid stigen, Jmt</t>
+          <t>t, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>525553</v>
+        <v>525477</v>
       </c>
       <c r="R42" t="n">
-        <v>7074694</v>
+        <v>7074713</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5306,12 +5307,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5320,6 +5321,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5338,7 +5340,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117243737</v>
+        <v>114532044</v>
       </c>
       <c r="B43" t="n">
         <v>58085</v>
@@ -5368,7 +5370,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -5381,17 +5383,17 @@
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>pölen, Jmt</t>
+          <t>vid stigen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>525444</v>
+        <v>525553</v>
       </c>
       <c r="R43" t="n">
-        <v>7074699</v>
+        <v>7074694</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5415,22 +5417,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5445,19 +5437,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118197285</v>
+        <v>117243737</v>
       </c>
       <c r="B44" t="n">
         <v>58085</v>
@@ -5490,6 +5482,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
@@ -5499,17 +5492,17 @@
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>45an, Jmt</t>
+          <t>pölen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>525458</v>
+        <v>525444</v>
       </c>
       <c r="R44" t="n">
-        <v>7074700</v>
+        <v>7074699</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5533,22 +5526,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5563,39 +5556,39 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121535633</v>
+        <v>118197285</v>
       </c>
       <c r="B45" t="n">
-        <v>56522</v>
+        <v>58085</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>206004</v>
+        <v>205976</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5603,12 +5596,15 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -5648,22 +5644,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5690,7 +5686,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130845229</v>
+        <v>121535633</v>
       </c>
       <c r="B46" t="n">
         <v>56522</v>
@@ -5729,17 +5725,17 @@
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>avlägg, Jmt</t>
+          <t>45an, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>525477</v>
+        <v>525458</v>
       </c>
       <c r="R46" t="n">
-        <v>7074694</v>
+        <v>7074700</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5763,12 +5759,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5783,39 +5789,39 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Nora Dahlström, Stefan Prenker</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135071023</v>
+        <v>130845229</v>
       </c>
       <c r="B47" t="n">
-        <v>58839</v>
+        <v>56522</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>208249</v>
+        <v>206004</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5823,15 +5829,14 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5869,12 +5874,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5883,7 +5888,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5902,7 +5906,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135234743</v>
+        <v>135071023</v>
       </c>
       <c r="B48" t="n">
         <v>58839</v>
@@ -5932,31 +5936,27 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>45an, Jmt</t>
+          <t>avlägg, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>525458</v>
+        <v>525477</v>
       </c>
       <c r="R48" t="n">
-        <v>7074700</v>
+        <v>7074694</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5980,12 +5980,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6001,22 +6001,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström, Stefan Prenker</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134600253</v>
+        <v>135234743</v>
       </c>
       <c r="B49" t="n">
-        <v>108205</v>
+        <v>58839</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6024,45 +6024,50 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220083</v>
+        <v>208249</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>brudborste, Jmt</t>
+          <t>45an, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>525446</v>
+        <v>525458</v>
       </c>
       <c r="R49" t="n">
-        <v>7074703</v>
+        <v>7074700</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6086,12 +6091,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6107,15 +6112,121 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
+          <t>Stefan Prenker</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Stefan Prenker</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>134600253</v>
+      </c>
+      <c r="B50" t="n">
+        <v>108205</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>brudborste, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>525446</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7074703</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
           <t>Nora Dahlström</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
+      <c r="AX50" t="inlineStr">
         <is>
           <t>Nora Dahlström, Stefan Prenker</t>
         </is>
       </c>
-      <c r="AY49" t="inlineStr"/>
+      <c r="AY50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AZ50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112943879</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122944137</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1009,6 +1024,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135234736</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1128,6 +1148,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111388908</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1237,6 +1262,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125991602</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1352,6 +1382,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118166153</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1467,6 +1502,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118166213</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1582,6 +1622,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118355065</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1697,6 +1742,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118355195</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1802,6 +1852,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118635758</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1917,6 +1972,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119317623</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2036,6 +2096,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125605376</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2151,6 +2216,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107420832</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2260,6 +2330,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112943997</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2369,6 +2444,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115140075</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2484,6 +2564,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121069884</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2603,6 +2688,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111991462</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2722,6 +2812,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116790485</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2841,6 +2936,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117156792</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2960,6 +3060,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711164</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3079,6 +3184,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116710218</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3188,6 +3298,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119607835</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3307,6 +3422,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118355322</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3426,6 +3546,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116710205</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3535,6 +3660,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126659326</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3644,6 +3774,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134208274</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3763,6 +3898,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456500</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3886,6 +4026,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117816937</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4005,6 +4150,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110849212</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4114,6 +4264,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119104405</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4223,6 +4378,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119389819</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4328,6 +4488,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129090796</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4437,6 +4602,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135235591</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4556,6 +4726,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115275704</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4665,6 +4840,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129540274</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4774,6 +4954,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129090663</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4893,6 +5078,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132177647</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5012,6 +5202,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133167590</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5119,6 +5314,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128105819</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5226,6 +5426,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135071522</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5337,6 +5542,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135545845</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5446,6 +5656,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114532044</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5565,6 +5780,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117243737</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5683,6 +5903,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118197285</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5798,6 +6023,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121535633</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5903,6 +6133,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130845229</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6010,6 +6245,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135071023</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6121,6 +6361,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135234743</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6227,8 +6472,64 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600253</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>135234736</v>
       </c>
       <c r="B4" t="n">
-        <v>57280</v>
+        <v>57285</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>135235591</v>
       </c>
       <c r="B34" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>135071522</v>
       </c>
       <c r="B41" t="n">
-        <v>43314</v>
+        <v>43319</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>135545845</v>
       </c>
       <c r="B42" t="n">
-        <v>43314</v>
+        <v>43319</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
         <v>135071023</v>
       </c>
       <c r="B48" t="n">
-        <v>58839</v>
+        <v>58844</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6256,7 +6256,7 @@
         <v>135234743</v>
       </c>
       <c r="B49" t="n">
-        <v>58839</v>
+        <v>58844</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ46"/>
+  <dimension ref="A1:AZ50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -918,27 +918,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111388908</v>
+        <v>135234736</v>
       </c>
       <c r="B4" t="n">
-        <v>58067</v>
+        <v>57285</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100090</v>
+        <v>100065</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nucifraga caryocatactes</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -961,14 +961,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>vid stigen, Jmt</t>
+          <t>45an, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525553</v>
+        <v>525458</v>
       </c>
       <c r="R4" t="n">
-        <v>7074694</v>
+        <v>7074700</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -995,22 +995,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-08-10</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-08-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,33 +1026,33 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111388908</t>
+          <t>https://artportalen.se/Sighting/135234736</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125991602</v>
+        <v>111388908</v>
       </c>
       <c r="B5" t="n">
-        <v>57825</v>
+        <v>58067</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100096</v>
+        <v>100090</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pandion haliaetus</t>
+          <t>Nucifraga caryocatactes</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1079,20 +1069,20 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>45an, Jmt</t>
+          <t>vid stigen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525458</v>
+        <v>525553</v>
       </c>
       <c r="R5" t="n">
-        <v>7074700</v>
+        <v>7074694</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1119,12 +1109,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2023-08-10</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2023-08-10</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,33 +1150,33 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125991602</t>
+          <t>https://artportalen.se/Sighting/111388908</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118166153</v>
+        <v>125991602</v>
       </c>
       <c r="B6" t="n">
-        <v>57953</v>
+        <v>57825</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100096</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1184,28 +1184,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>t, Jmt</t>
+          <t>45an, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>525477</v>
+        <v>525458</v>
       </c>
       <c r="R6" t="n">
-        <v>7074713</v>
+        <v>7074700</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1229,22 +1233,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,13 +1264,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118166153</t>
+          <t>https://artportalen.se/Sighting/125991602</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118166213</v>
+        <v>118166153</v>
       </c>
       <c r="B7" t="n">
         <v>57953</v>
@@ -1319,10 +1313,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>525499</v>
+        <v>525477</v>
       </c>
       <c r="R7" t="n">
-        <v>7074704</v>
+        <v>7074713</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1390,13 +1384,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118166213</t>
+          <t>https://artportalen.se/Sighting/118166153</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118355065</v>
+        <v>118166213</v>
       </c>
       <c r="B8" t="n">
         <v>57953</v>
@@ -1439,10 +1433,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>525507</v>
+        <v>525499</v>
       </c>
       <c r="R8" t="n">
-        <v>7074702</v>
+        <v>7074704</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1469,7 +1463,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -1479,7 +1473,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1510,13 +1504,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118355065</t>
+          <t>https://artportalen.se/Sighting/118166213</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118355195</v>
+        <v>118355065</v>
       </c>
       <c r="B9" t="n">
         <v>57953</v>
@@ -1559,10 +1553,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525516</v>
+        <v>525507</v>
       </c>
       <c r="R9" t="n">
-        <v>7074704</v>
+        <v>7074702</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1630,13 +1624,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118355195</t>
+          <t>https://artportalen.se/Sighting/118355065</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118635758</v>
+        <v>118355195</v>
       </c>
       <c r="B10" t="n">
         <v>57953</v>
@@ -1675,17 +1669,17 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>avlägg, Jmt</t>
+          <t>t, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>525477</v>
+        <v>525516</v>
       </c>
       <c r="R10" t="n">
-        <v>7074694</v>
+        <v>7074704</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1709,12 +1703,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-10</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-10</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1729,24 +1733,24 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118635758</t>
+          <t>https://artportalen.se/Sighting/118355195</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119317623</v>
+        <v>118635758</v>
       </c>
       <c r="B11" t="n">
         <v>57953</v>
@@ -1785,17 +1789,17 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>vid stigen, Jmt</t>
+          <t>avlägg, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>525553</v>
+        <v>525477</v>
       </c>
       <c r="R11" t="n">
         <v>7074694</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1819,22 +1823,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1849,24 +1843,24 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119317623</t>
+          <t>https://artportalen.se/Sighting/118635758</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125605376</v>
+        <v>119317623</v>
       </c>
       <c r="B12" t="n">
         <v>57953</v>
@@ -1894,32 +1888,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>bnm, Jmt</t>
+          <t>vid stigen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>525550</v>
+        <v>525553</v>
       </c>
       <c r="R12" t="n">
-        <v>7074647</v>
+        <v>7074694</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1943,22 +1933,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1973,73 +1963,77 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Nora Dahlström, Stefan Prenker</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125605376</t>
+          <t>https://artportalen.se/Sighting/119317623</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>107420832</v>
+        <v>125605376</v>
       </c>
       <c r="B13" t="n">
-        <v>57141</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>vid stigen, Jmt</t>
+          <t>bnm, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>525553</v>
+        <v>525550</v>
       </c>
       <c r="R13" t="n">
-        <v>7074694</v>
+        <v>7074647</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2063,22 +2057,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-03-20</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-03-20</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2093,27 +2087,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström, Stefan Prenker</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/107420832</t>
+          <t>https://artportalen.se/Sighting/125605376</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112943997</v>
+        <v>107420832</v>
       </c>
       <c r="B14" t="n">
-        <v>58592</v>
+        <v>57141</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2121,33 +2115,29 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102125</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2187,12 +2177,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-03-20</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-03-20</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2218,16 +2218,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112943997</t>
+          <t>https://artportalen.se/Sighting/107420832</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>115140075</v>
+        <v>112943997</v>
       </c>
       <c r="B15" t="n">
-        <v>57132</v>
+        <v>58592</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2235,16 +2235,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102612</v>
+        <v>102125</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2254,14 +2254,14 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2301,12 +2301,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2332,13 +2332,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115140075</t>
+          <t>https://artportalen.se/Sighting/112943997</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121069884</v>
+        <v>115140075</v>
       </c>
       <c r="B16" t="n">
         <v>57132</v>
@@ -2366,7 +2366,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
@@ -2377,17 +2381,17 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>avlägg, Jmt</t>
+          <t>vid stigen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>525477</v>
+        <v>525553</v>
       </c>
       <c r="R16" t="n">
         <v>7074694</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2411,22 +2415,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>13:40</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:40</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2441,27 +2435,27 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121069884</t>
+          <t>https://artportalen.se/Sighting/115140075</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>111991462</v>
+        <v>121069884</v>
       </c>
       <c r="B17" t="n">
-        <v>57144</v>
+        <v>57132</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2469,16 +2463,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102613</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2486,32 +2480,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>vid stigen, Jmt</t>
+          <t>avlägg, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>525553</v>
+        <v>525477</v>
       </c>
       <c r="R17" t="n">
         <v>7074694</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2535,22 +2525,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2565,49 +2555,49 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111991462</t>
+          <t>https://artportalen.se/Sighting/121069884</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>116790485</v>
+        <v>111991462</v>
       </c>
       <c r="B18" t="n">
-        <v>57369</v>
+        <v>57144</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102961</v>
+        <v>102613</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2619,23 +2609,23 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>pölen, Jmt</t>
+          <t>vid stigen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>525444</v>
+        <v>525553</v>
       </c>
       <c r="R18" t="n">
-        <v>7074699</v>
+        <v>7074694</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2659,22 +2649,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2689,24 +2679,24 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116790485</t>
+          <t>https://artportalen.se/Sighting/111991462</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117156792</v>
+        <v>116790485</v>
       </c>
       <c r="B19" t="n">
         <v>57369</v>
@@ -2736,7 +2726,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -2749,17 +2739,17 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>45an, Jmt</t>
+          <t>pölen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>525458</v>
+        <v>525444</v>
       </c>
       <c r="R19" t="n">
-        <v>7074700</v>
+        <v>7074699</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2783,17 +2773,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -2813,24 +2803,24 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117156792</t>
+          <t>https://artportalen.se/Sighting/116790485</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117711164</v>
+        <v>117156792</v>
       </c>
       <c r="B20" t="n">
         <v>57369</v>
@@ -2867,23 +2857,23 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>avlägg, Jmt</t>
+          <t>45an, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>525477</v>
+        <v>525458</v>
       </c>
       <c r="R20" t="n">
-        <v>7074694</v>
+        <v>7074700</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2907,22 +2897,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2937,27 +2927,27 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117711164</t>
+          <t>https://artportalen.se/Sighting/117156792</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>116710218</v>
+        <v>117711164</v>
       </c>
       <c r="B21" t="n">
-        <v>58541</v>
+        <v>57369</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2965,16 +2955,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102987</v>
+        <v>102961</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sädesärla</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Motacilla alba</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2991,23 +2981,23 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>45an, Jmt</t>
+          <t>avlägg, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>525458</v>
+        <v>525477</v>
       </c>
       <c r="R21" t="n">
-        <v>7074700</v>
+        <v>7074694</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3031,22 +3021,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3061,24 +3051,24 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116710218</t>
+          <t>https://artportalen.se/Sighting/117711164</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119607835</v>
+        <v>116710218</v>
       </c>
       <c r="B22" t="n">
         <v>58541</v>
@@ -3121,17 +3111,17 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>avlägg, Jmt</t>
+          <t>45an, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>525477</v>
+        <v>525458</v>
       </c>
       <c r="R22" t="n">
-        <v>7074694</v>
+        <v>7074700</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3155,12 +3145,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-05-08</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-05-08</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3175,27 +3175,27 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119607835</t>
+          <t>https://artportalen.se/Sighting/116710218</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118355322</v>
+        <v>119607835</v>
       </c>
       <c r="B23" t="n">
-        <v>58393</v>
+        <v>58541</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3203,16 +3203,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102999</v>
+        <v>102987</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3222,30 +3222,30 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>45an, Jmt</t>
+          <t>avlägg, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>525458</v>
+        <v>525477</v>
       </c>
       <c r="R23" t="n">
-        <v>7074700</v>
+        <v>7074694</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3269,22 +3269,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3299,27 +3289,27 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118355322</t>
+          <t>https://artportalen.se/Sighting/119607835</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>116710205</v>
+        <v>118355322</v>
       </c>
       <c r="B24" t="n">
-        <v>58388</v>
+        <v>58393</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3327,33 +3317,33 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103001</v>
+        <v>102999</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3393,22 +3383,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3434,50 +3424,50 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116710205</t>
+          <t>https://artportalen.se/Sighting/118355322</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126659326</v>
+        <v>116710205</v>
       </c>
       <c r="B25" t="n">
-        <v>58286</v>
+        <v>58388</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103008</v>
+        <v>103001</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3517,12 +3507,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2024-05-08</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2024-05-08</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3542,22 +3542,22 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Stefan Prenker, Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126659326</t>
+          <t>https://artportalen.se/Sighting/116710205</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134208274</v>
+        <v>126659326</v>
       </c>
       <c r="B26" t="n">
-        <v>58349</v>
+        <v>58286</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3565,16 +3565,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>103008</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3591,7 +3591,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3631,12 +3631,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2025-07-13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2025-07-13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3662,13 +3662,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134208274</t>
+          <t>https://artportalen.se/Sighting/126659326</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134456500</v>
+        <v>134208274</v>
       </c>
       <c r="B27" t="n">
         <v>58349</v>
@@ -3705,20 +3705,20 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>vid stigen, Jmt</t>
+          <t>45an, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>525553</v>
+        <v>525458</v>
       </c>
       <c r="R27" t="n">
-        <v>7074694</v>
+        <v>7074700</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3745,22 +3745,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3786,16 +3776,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134456500</t>
+          <t>https://artportalen.se/Sighting/134208274</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117816937</v>
+        <v>134456500</v>
       </c>
       <c r="B28" t="n">
-        <v>58439</v>
+        <v>58349</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3803,21 +3793,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3826,27 +3816,23 @@
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>45an, Jmt</t>
+          <t>vid stigen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>525458</v>
+        <v>525553</v>
       </c>
       <c r="R28" t="n">
-        <v>7074700</v>
+        <v>7074694</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3873,22 +3859,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3908,44 +3894,44 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Stefan Prenker, Nora Dahlström</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117816937</t>
+          <t>https://artportalen.se/Sighting/134456500</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>110849212</v>
+        <v>117816937</v>
       </c>
       <c r="B29" t="n">
-        <v>58114</v>
+        <v>58439</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>103018</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3954,23 +3940,27 @@
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>vid stigen, Jmt</t>
+          <t>45an, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>525553</v>
+        <v>525458</v>
       </c>
       <c r="R29" t="n">
-        <v>7074694</v>
+        <v>7074700</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3997,22 +3987,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2023-07-15</t>
+          <t>2024-06-16</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2023-07-15</t>
+          <t>2024-06-16</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4038,13 +4028,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110849212</t>
+          <t>https://artportalen.se/Sighting/117816937</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119104405</v>
+        <v>110849212</v>
       </c>
       <c r="B30" t="n">
         <v>58114</v>
@@ -4074,27 +4064,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>45an, Jmt</t>
+          <t>vid stigen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>525458</v>
+        <v>525553</v>
       </c>
       <c r="R30" t="n">
-        <v>7074700</v>
+        <v>7074694</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4121,12 +4111,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2023-07-15</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2023-07-15</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4152,13 +4152,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119104405</t>
+          <t>https://artportalen.se/Sighting/110849212</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119389819</v>
+        <v>119104405</v>
       </c>
       <c r="B31" t="n">
         <v>58114</v>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -4201,17 +4201,17 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>avlägg, Jmt</t>
+          <t>45an, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>525477</v>
+        <v>525458</v>
       </c>
       <c r="R31" t="n">
-        <v>7074694</v>
+        <v>7074700</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4235,12 +4235,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4255,24 +4255,24 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119389819</t>
+          <t>https://artportalen.se/Sighting/119104405</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129090796</v>
+        <v>119389819</v>
       </c>
       <c r="B32" t="n">
         <v>58114</v>
@@ -4300,25 +4300,29 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>bnm, Jmt</t>
+          <t>avlägg, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>525550</v>
+        <v>525477</v>
       </c>
       <c r="R32" t="n">
-        <v>7074647</v>
+        <v>7074694</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4345,12 +4349,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4376,16 +4380,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129090796</t>
+          <t>https://artportalen.se/Sighting/119389819</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>115275704</v>
+        <v>129090796</v>
       </c>
       <c r="B33" t="n">
-        <v>58057</v>
+        <v>58114</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4393,49 +4397,45 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>vid stigen, Jmt</t>
+          <t>bnm, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>525553</v>
+        <v>525550</v>
       </c>
       <c r="R33" t="n">
-        <v>7074694</v>
+        <v>7074647</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4459,22 +4459,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4489,27 +4479,27 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115275704</t>
+          <t>https://artportalen.se/Sighting/129090796</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129540274</v>
+        <v>135235591</v>
       </c>
       <c r="B34" t="n">
-        <v>58057</v>
+        <v>58141</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4517,49 +4507,49 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>45an, Jmt</t>
+          <t>kj, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>525458</v>
+        <v>525528</v>
       </c>
       <c r="R34" t="n">
-        <v>7074700</v>
+        <v>7074639</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4583,12 +4573,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4603,49 +4593,49 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Stefan Prenker, Nora Dahlström</t>
+          <t>Nora Dahlström, Stefan Prenker</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129540274</t>
+          <t>https://artportalen.se/Sighting/135235591</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129090663</v>
+        <v>115275704</v>
       </c>
       <c r="B35" t="n">
-        <v>58082</v>
+        <v>58057</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103035</v>
+        <v>103031</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4657,23 +4647,23 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>avlägg, Jmt</t>
+          <t>vid stigen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>525477</v>
+        <v>525553</v>
       </c>
       <c r="R35" t="n">
         <v>7074694</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4697,12 +4687,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2024-03-19</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2024-03-19</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4717,44 +4717,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129090663</t>
+          <t>https://artportalen.se/Sighting/115275704</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132177647</v>
+        <v>129540274</v>
       </c>
       <c r="B36" t="n">
-        <v>58624</v>
+        <v>58057</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103042</v>
+        <v>103031</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4764,14 +4764,14 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4811,22 +4811,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4852,16 +4842,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132177647</t>
+          <t>https://artportalen.se/Sighting/129540274</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133167590</v>
+        <v>129090663</v>
       </c>
       <c r="B37" t="n">
-        <v>58658</v>
+        <v>58082</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4869,49 +4859,49 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103044</v>
+        <v>103035</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Corvus corone</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>vid stigen, Jmt</t>
+          <t>avlägg, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>525553</v>
+        <v>525477</v>
       </c>
       <c r="R37" t="n">
         <v>7074694</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4935,22 +4925,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4965,44 +4945,44 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Stefan Prenker, Nora Dahlström</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133167590</t>
+          <t>https://artportalen.se/Sighting/129090663</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128105819</v>
+        <v>132177647</v>
       </c>
       <c r="B38" t="n">
-        <v>43258</v>
+        <v>58624</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>201129</v>
+        <v>103042</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitfläckig guldvinge</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycaena virgaureae</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -5015,24 +4995,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>avlägg, Jmt</t>
+          <t>45an, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>525477</v>
+        <v>525458</v>
       </c>
       <c r="R38" t="n">
-        <v>7074694</v>
+        <v>7074700</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5056,12 +5039,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5070,81 +5063,83 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Nora Dahlström, Stefan Prenker</t>
+          <t>Stefan Prenker, Nora Dahlström</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128105819</t>
+          <t>https://artportalen.se/Sighting/132177647</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135071522</v>
+        <v>133167590</v>
       </c>
       <c r="B39" t="n">
-        <v>43319</v>
+        <v>58658</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>201146</v>
+        <v>103044</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Silverblåvinge</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Polyommatus amandus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schneider, 1792)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>avlägg, Jmt</t>
+          <t>vid stigen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>525477</v>
+        <v>525553</v>
       </c>
       <c r="R39" t="n">
         <v>7074694</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5168,12 +5163,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5182,84 +5187,80 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Nora Dahlström, Stefan Prenker</t>
+          <t>Stefan Prenker, Nora Dahlström</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135071522</t>
+          <t>https://artportalen.se/Sighting/133167590</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>114532044</v>
+        <v>128105819</v>
       </c>
       <c r="B40" t="n">
-        <v>58085</v>
+        <v>43258</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>205976</v>
+        <v>201129</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Vitfläckig guldvinge</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Lycaena virgaureae</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>vid stigen, Jmt</t>
+          <t>avlägg, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>525553</v>
+        <v>525477</v>
       </c>
       <c r="R40" t="n">
         <v>7074694</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5283,12 +5284,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5297,55 +5298,56 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström, Stefan Prenker</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114532044</t>
+          <t>https://artportalen.se/Sighting/128105819</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117243737</v>
+        <v>135071522</v>
       </c>
       <c r="B41" t="n">
-        <v>58085</v>
+        <v>43319</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>205976</v>
+        <v>201146</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Silverblåvinge</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Polyommatus amandus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schneider, 1792)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5353,24 +5355,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>pölen, Jmt</t>
+          <t>avlägg, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>525444</v>
+        <v>525477</v>
       </c>
       <c r="R41" t="n">
-        <v>7074699</v>
+        <v>7074694</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5397,22 +5396,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5421,6 +5410,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5432,44 +5422,44 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Nora Dahlström, Stefan Prenker</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117243737</t>
+          <t>https://artportalen.se/Sighting/135071522</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118197285</v>
+        <v>135545845</v>
       </c>
       <c r="B42" t="n">
-        <v>58085</v>
+        <v>43319</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>205976</v>
+        <v>201146</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Silverblåvinge</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Polyommatus amandus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schneider, 1792)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5477,26 +5467,28 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>45an, Jmt</t>
+          <t>t, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>525458</v>
+        <v>525477</v>
       </c>
       <c r="R42" t="n">
-        <v>7074700</v>
+        <v>7074713</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5520,22 +5512,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5544,6 +5526,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5561,33 +5544,33 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118197285</t>
+          <t>https://artportalen.se/Sighting/135545845</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121535633</v>
+        <v>114532044</v>
       </c>
       <c r="B43" t="n">
-        <v>56522</v>
+        <v>58085</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>206004</v>
+        <v>205976</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5595,25 +5578,29 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>45an, Jmt</t>
+          <t>vid stigen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>525458</v>
+        <v>525553</v>
       </c>
       <c r="R43" t="n">
-        <v>7074700</v>
+        <v>7074694</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5640,22 +5627,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5681,33 +5658,33 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121535633</t>
+          <t>https://artportalen.se/Sighting/114532044</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130845229</v>
+        <v>117243737</v>
       </c>
       <c r="B44" t="n">
-        <v>56522</v>
+        <v>58085</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>206004</v>
+        <v>205976</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5715,25 +5692,29 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>avlägg, Jmt</t>
+          <t>pölen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>525477</v>
+        <v>525444</v>
       </c>
       <c r="R44" t="n">
-        <v>7074694</v>
+        <v>7074699</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5760,12 +5741,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5785,22 +5776,22 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Nora Dahlström, Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130845229</t>
+          <t>https://artportalen.se/Sighting/117243737</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135071023</v>
+        <v>118197285</v>
       </c>
       <c r="B45" t="n">
-        <v>58844</v>
+        <v>58085</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5808,16 +5799,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>208249</v>
+        <v>205976</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5830,24 +5821,26 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>avlägg, Jmt</t>
+          <t>45an, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>525477</v>
+        <v>525458</v>
       </c>
       <c r="R45" t="n">
-        <v>7074694</v>
+        <v>7074700</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5871,12 +5864,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5885,80 +5888,79 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Nora Dahlström, Stefan Prenker</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135071023</t>
+          <t>https://artportalen.se/Sighting/118197285</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134600253</v>
+        <v>121535633</v>
       </c>
       <c r="B46" t="n">
-        <v>108205</v>
+        <v>56522</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220083</v>
+        <v>206004</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>brudborste, Jmt</t>
+          <t>45an, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>525446</v>
+        <v>525458</v>
       </c>
       <c r="R46" t="n">
-        <v>7074703</v>
+        <v>7074700</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5982,12 +5984,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5996,23 +6008,471 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Nora Dahlström, Stefan Prenker</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121535633</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>130845229</v>
+      </c>
+      <c r="B47" t="n">
+        <v>56522</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>avlägg, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>525477</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7074694</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Nora Dahlström</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Nora Dahlström, Stefan Prenker</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130845229</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135071023</v>
+      </c>
+      <c r="B48" t="n">
+        <v>58844</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>avlägg, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>525477</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7074694</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Nora Dahlström</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Nora Dahlström, Stefan Prenker</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135071023</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>135234743</v>
+      </c>
+      <c r="B49" t="n">
+        <v>58844</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>45an, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>525458</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7074700</v>
+      </c>
+      <c r="S49" t="n">
+        <v>25</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Stefan Prenker</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Stefan Prenker</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135234743</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>134600253</v>
+      </c>
+      <c r="B50" t="n">
+        <v>108205</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>brudborste, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>525446</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7074703</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Nora Dahlström</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Nora Dahlström, Stefan Prenker</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134600253</t>
         </is>
@@ -6065,6 +6525,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ50"/>
+  <dimension ref="A1:AZ51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2104,32 +2104,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>107420832</v>
+        <v>136036391</v>
       </c>
       <c r="B14" t="n">
-        <v>57141</v>
+        <v>57982</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2137,23 +2137,23 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>vid stigen, Jmt</t>
+          <t>kj, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>525553</v>
+        <v>525528</v>
       </c>
       <c r="R14" t="n">
-        <v>7074694</v>
+        <v>7074639</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2177,22 +2177,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-03-20</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-03-20</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2207,27 +2202,27 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström, Stefan Prenker</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/107420832</t>
+          <t>https://artportalen.se/Sighting/136036391</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112943997</v>
+        <v>107420832</v>
       </c>
       <c r="B15" t="n">
-        <v>58592</v>
+        <v>57141</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2235,33 +2230,29 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102125</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2301,12 +2292,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-03-20</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-03-20</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2332,16 +2333,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112943997</t>
+          <t>https://artportalen.se/Sighting/107420832</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>115140075</v>
+        <v>112943997</v>
       </c>
       <c r="B16" t="n">
-        <v>57132</v>
+        <v>58592</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2349,16 +2350,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>102125</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2368,14 +2369,14 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2415,12 +2416,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2446,13 +2447,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115140075</t>
+          <t>https://artportalen.se/Sighting/112943997</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121069884</v>
+        <v>115140075</v>
       </c>
       <c r="B17" t="n">
         <v>57132</v>
@@ -2480,7 +2481,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
@@ -2491,17 +2496,17 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>avlägg, Jmt</t>
+          <t>vid stigen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>525477</v>
+        <v>525553</v>
       </c>
       <c r="R17" t="n">
         <v>7074694</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2525,22 +2530,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>13:40</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>13:40</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2555,27 +2550,27 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121069884</t>
+          <t>https://artportalen.se/Sighting/115140075</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>111991462</v>
+        <v>121069884</v>
       </c>
       <c r="B18" t="n">
-        <v>57144</v>
+        <v>57132</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2583,16 +2578,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102613</v>
+        <v>102612</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2600,32 +2595,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>vid stigen, Jmt</t>
+          <t>avlägg, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>525553</v>
+        <v>525477</v>
       </c>
       <c r="R18" t="n">
         <v>7074694</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2649,22 +2640,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2679,49 +2670,49 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111991462</t>
+          <t>https://artportalen.se/Sighting/121069884</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>116790485</v>
+        <v>111991462</v>
       </c>
       <c r="B19" t="n">
-        <v>57369</v>
+        <v>57144</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102961</v>
+        <v>102613</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2733,23 +2724,23 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>pölen, Jmt</t>
+          <t>vid stigen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>525444</v>
+        <v>525553</v>
       </c>
       <c r="R19" t="n">
-        <v>7074699</v>
+        <v>7074694</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2773,22 +2764,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2803,24 +2794,24 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116790485</t>
+          <t>https://artportalen.se/Sighting/111991462</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117156792</v>
+        <v>116790485</v>
       </c>
       <c r="B20" t="n">
         <v>57369</v>
@@ -2850,7 +2841,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -2863,17 +2854,17 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>45an, Jmt</t>
+          <t>pölen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>525458</v>
+        <v>525444</v>
       </c>
       <c r="R20" t="n">
-        <v>7074700</v>
+        <v>7074699</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2897,17 +2888,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -2927,24 +2918,24 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117156792</t>
+          <t>https://artportalen.se/Sighting/116790485</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117711164</v>
+        <v>117156792</v>
       </c>
       <c r="B21" t="n">
         <v>57369</v>
@@ -2981,23 +2972,23 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>avlägg, Jmt</t>
+          <t>45an, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>525477</v>
+        <v>525458</v>
       </c>
       <c r="R21" t="n">
-        <v>7074694</v>
+        <v>7074700</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3021,22 +3012,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3051,27 +3042,27 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117711164</t>
+          <t>https://artportalen.se/Sighting/117156792</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>116710218</v>
+        <v>117711164</v>
       </c>
       <c r="B22" t="n">
-        <v>58541</v>
+        <v>57369</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3079,16 +3070,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102987</v>
+        <v>102961</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sädesärla</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Motacilla alba</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3105,23 +3096,23 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>45an, Jmt</t>
+          <t>avlägg, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>525458</v>
+        <v>525477</v>
       </c>
       <c r="R22" t="n">
-        <v>7074700</v>
+        <v>7074694</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3145,22 +3136,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3175,24 +3166,24 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116710218</t>
+          <t>https://artportalen.se/Sighting/117711164</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119607835</v>
+        <v>116710218</v>
       </c>
       <c r="B23" t="n">
         <v>58541</v>
@@ -3235,17 +3226,17 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>avlägg, Jmt</t>
+          <t>45an, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>525477</v>
+        <v>525458</v>
       </c>
       <c r="R23" t="n">
-        <v>7074694</v>
+        <v>7074700</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3269,12 +3260,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-05-08</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-05-08</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3289,27 +3290,27 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119607835</t>
+          <t>https://artportalen.se/Sighting/116710218</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118355322</v>
+        <v>119607835</v>
       </c>
       <c r="B24" t="n">
-        <v>58393</v>
+        <v>58541</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3317,16 +3318,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102999</v>
+        <v>102987</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3336,30 +3337,30 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>45an, Jmt</t>
+          <t>avlägg, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>525458</v>
+        <v>525477</v>
       </c>
       <c r="R24" t="n">
-        <v>7074700</v>
+        <v>7074694</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3383,22 +3384,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3413,27 +3404,27 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118355322</t>
+          <t>https://artportalen.se/Sighting/119607835</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>116710205</v>
+        <v>118355322</v>
       </c>
       <c r="B25" t="n">
-        <v>58388</v>
+        <v>58393</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3441,33 +3432,33 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103001</v>
+        <v>102999</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3507,22 +3498,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3548,50 +3539,50 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116710205</t>
+          <t>https://artportalen.se/Sighting/118355322</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126659326</v>
+        <v>116710205</v>
       </c>
       <c r="B26" t="n">
-        <v>58286</v>
+        <v>58388</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103008</v>
+        <v>103001</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3631,12 +3622,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2024-05-08</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2024-05-08</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3656,22 +3657,22 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Stefan Prenker, Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126659326</t>
+          <t>https://artportalen.se/Sighting/116710205</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134208274</v>
+        <v>126659326</v>
       </c>
       <c r="B27" t="n">
-        <v>58349</v>
+        <v>58286</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3679,16 +3680,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103015</v>
+        <v>103008</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3705,7 +3706,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3745,12 +3746,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2025-07-13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2025-07-13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3776,13 +3777,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134208274</t>
+          <t>https://artportalen.se/Sighting/126659326</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134456500</v>
+        <v>134208274</v>
       </c>
       <c r="B28" t="n">
         <v>58349</v>
@@ -3819,20 +3820,20 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>vid stigen, Jmt</t>
+          <t>45an, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>525553</v>
+        <v>525458</v>
       </c>
       <c r="R28" t="n">
-        <v>7074694</v>
+        <v>7074700</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3859,22 +3860,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3900,16 +3891,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134456500</t>
+          <t>https://artportalen.se/Sighting/134208274</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117816937</v>
+        <v>134456500</v>
       </c>
       <c r="B29" t="n">
-        <v>58439</v>
+        <v>58349</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3917,21 +3908,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3940,27 +3931,23 @@
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>45an, Jmt</t>
+          <t>vid stigen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>525458</v>
+        <v>525553</v>
       </c>
       <c r="R29" t="n">
-        <v>7074700</v>
+        <v>7074694</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3987,22 +3974,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4022,44 +4009,44 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Stefan Prenker, Nora Dahlström</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117816937</t>
+          <t>https://artportalen.se/Sighting/134456500</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>110849212</v>
+        <v>117816937</v>
       </c>
       <c r="B30" t="n">
-        <v>58114</v>
+        <v>58439</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>103018</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -4068,23 +4055,27 @@
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>vid stigen, Jmt</t>
+          <t>45an, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>525553</v>
+        <v>525458</v>
       </c>
       <c r="R30" t="n">
-        <v>7074694</v>
+        <v>7074700</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4111,22 +4102,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2023-07-15</t>
+          <t>2024-06-16</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2023-07-15</t>
+          <t>2024-06-16</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4152,13 +4143,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110849212</t>
+          <t>https://artportalen.se/Sighting/117816937</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119104405</v>
+        <v>110849212</v>
       </c>
       <c r="B31" t="n">
         <v>58114</v>
@@ -4188,27 +4179,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>45an, Jmt</t>
+          <t>vid stigen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>525458</v>
+        <v>525553</v>
       </c>
       <c r="R31" t="n">
-        <v>7074700</v>
+        <v>7074694</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4235,12 +4226,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2023-07-15</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2023-07-15</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4266,13 +4267,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119104405</t>
+          <t>https://artportalen.se/Sighting/110849212</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119389819</v>
+        <v>119104405</v>
       </c>
       <c r="B32" t="n">
         <v>58114</v>
@@ -4302,7 +4303,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -4315,17 +4316,17 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>avlägg, Jmt</t>
+          <t>45an, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>525477</v>
+        <v>525458</v>
       </c>
       <c r="R32" t="n">
-        <v>7074694</v>
+        <v>7074700</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4349,12 +4350,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4369,24 +4370,24 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119389819</t>
+          <t>https://artportalen.se/Sighting/119104405</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129090796</v>
+        <v>119389819</v>
       </c>
       <c r="B33" t="n">
         <v>58114</v>
@@ -4414,25 +4415,29 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>bnm, Jmt</t>
+          <t>avlägg, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>525550</v>
+        <v>525477</v>
       </c>
       <c r="R33" t="n">
-        <v>7074647</v>
+        <v>7074694</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4459,12 +4464,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4490,16 +4495,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129090796</t>
+          <t>https://artportalen.se/Sighting/119389819</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135235591</v>
+        <v>129090796</v>
       </c>
       <c r="B34" t="n">
-        <v>58141</v>
+        <v>58114</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4524,11 +4529,7 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
@@ -4539,14 +4540,14 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>kj, Jmt</t>
+          <t>bnm, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>525528</v>
+        <v>525550</v>
       </c>
       <c r="R34" t="n">
-        <v>7074639</v>
+        <v>7074647</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4573,12 +4574,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4598,22 +4599,22 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Nora Dahlström, Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135235591</t>
+          <t>https://artportalen.se/Sighting/129090796</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>115275704</v>
+        <v>135235591</v>
       </c>
       <c r="B35" t="n">
-        <v>58057</v>
+        <v>58141</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4621,49 +4622,49 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>vid stigen, Jmt</t>
+          <t>kj, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>525553</v>
+        <v>525528</v>
       </c>
       <c r="R35" t="n">
-        <v>7074694</v>
+        <v>7074639</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4687,22 +4688,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4717,24 +4708,24 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström, Stefan Prenker</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115275704</t>
+          <t>https://artportalen.se/Sighting/135235591</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129540274</v>
+        <v>115275704</v>
       </c>
       <c r="B36" t="n">
         <v>58057</v>
@@ -4771,20 +4762,20 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>45an, Jmt</t>
+          <t>vid stigen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>525458</v>
+        <v>525553</v>
       </c>
       <c r="R36" t="n">
-        <v>7074700</v>
+        <v>7074694</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4811,12 +4802,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2024-03-19</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2024-03-19</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4836,44 +4837,44 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Stefan Prenker, Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129540274</t>
+          <t>https://artportalen.se/Sighting/115275704</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129090663</v>
+        <v>129540274</v>
       </c>
       <c r="B37" t="n">
-        <v>58082</v>
+        <v>58057</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103035</v>
+        <v>103031</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4885,23 +4886,23 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>avlägg, Jmt</t>
+          <t>45an, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>525477</v>
+        <v>525458</v>
       </c>
       <c r="R37" t="n">
-        <v>7074694</v>
+        <v>7074700</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4925,12 +4926,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4945,54 +4946,54 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker, Nora Dahlström</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129090663</t>
+          <t>https://artportalen.se/Sighting/129540274</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132177647</v>
+        <v>129090663</v>
       </c>
       <c r="B38" t="n">
-        <v>58624</v>
+        <v>58082</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103042</v>
+        <v>103035</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Corvus corone</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -5005,17 +5006,17 @@
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>45an, Jmt</t>
+          <t>avlägg, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>525458</v>
+        <v>525477</v>
       </c>
       <c r="R38" t="n">
-        <v>7074700</v>
+        <v>7074694</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5039,22 +5040,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5069,44 +5060,44 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Stefan Prenker, Nora Dahlström</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132177647</t>
+          <t>https://artportalen.se/Sighting/129090663</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133167590</v>
+        <v>132177647</v>
       </c>
       <c r="B39" t="n">
-        <v>58658</v>
+        <v>58624</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103044</v>
+        <v>103042</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -5116,27 +5107,27 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>vid stigen, Jmt</t>
+          <t>45an, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>525553</v>
+        <v>525458</v>
       </c>
       <c r="R39" t="n">
-        <v>7074694</v>
+        <v>7074700</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5163,22 +5154,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5204,33 +5195,33 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133167590</t>
+          <t>https://artportalen.se/Sighting/132177647</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128105819</v>
+        <v>133167590</v>
       </c>
       <c r="B40" t="n">
-        <v>43258</v>
+        <v>58658</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>201129</v>
+        <v>103044</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitfläckig guldvinge</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lycaena virgaureae</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5240,27 +5231,30 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>avlägg, Jmt</t>
+          <t>vid stigen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>525477</v>
+        <v>525553</v>
       </c>
       <c r="R40" t="n">
         <v>7074694</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5284,12 +5278,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5298,56 +5302,55 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Nora Dahlström, Stefan Prenker</t>
+          <t>Stefan Prenker, Nora Dahlström</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128105819</t>
+          <t>https://artportalen.se/Sighting/133167590</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135071522</v>
+        <v>128105819</v>
       </c>
       <c r="B41" t="n">
-        <v>43319</v>
+        <v>43258</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>201146</v>
+        <v>201129</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Silverblåvinge</t>
+          <t>Vitfläckig guldvinge</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Polyommatus amandus</t>
+          <t>Lycaena virgaureae</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schneider, 1792)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5396,12 +5399,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5428,13 +5431,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135071522</t>
+          <t>https://artportalen.se/Sighting/128105819</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135545845</v>
+        <v>135071522</v>
       </c>
       <c r="B42" t="n">
         <v>43319</v>
@@ -5470,25 +5473,21 @@
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>t, Jmt</t>
+          <t>avlägg, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
         <v>525477</v>
       </c>
       <c r="R42" t="n">
-        <v>7074713</v>
+        <v>7074694</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5512,12 +5511,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5533,77 +5532,78 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström, Stefan Prenker</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135545845</t>
+          <t>https://artportalen.se/Sighting/135071522</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>114532044</v>
+        <v>135545845</v>
       </c>
       <c r="B43" t="n">
-        <v>58085</v>
+        <v>43319</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>205976</v>
+        <v>201146</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Silverblåvinge</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Polyommatus amandus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schneider, 1792)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>vid stigen, Jmt</t>
+          <t>t, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>525553</v>
+        <v>525477</v>
       </c>
       <c r="R43" t="n">
-        <v>7074694</v>
+        <v>7074713</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5627,12 +5627,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5641,6 +5641,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5658,13 +5659,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114532044</t>
+          <t>https://artportalen.se/Sighting/135545845</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117243737</v>
+        <v>114532044</v>
       </c>
       <c r="B44" t="n">
         <v>58085</v>
@@ -5694,7 +5695,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -5707,17 +5708,17 @@
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>pölen, Jmt</t>
+          <t>vid stigen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>525444</v>
+        <v>525553</v>
       </c>
       <c r="R44" t="n">
-        <v>7074699</v>
+        <v>7074694</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5741,22 +5742,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5771,24 +5762,24 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117243737</t>
+          <t>https://artportalen.se/Sighting/114532044</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118197285</v>
+        <v>117243737</v>
       </c>
       <c r="B45" t="n">
         <v>58085</v>
@@ -5821,6 +5812,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
@@ -5830,17 +5822,17 @@
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>45an, Jmt</t>
+          <t>pölen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>525458</v>
+        <v>525444</v>
       </c>
       <c r="R45" t="n">
-        <v>7074700</v>
+        <v>7074699</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5864,22 +5856,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5894,44 +5886,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118197285</t>
+          <t>https://artportalen.se/Sighting/117243737</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121535633</v>
+        <v>118197285</v>
       </c>
       <c r="B46" t="n">
-        <v>56522</v>
+        <v>58085</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>206004</v>
+        <v>205976</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5939,12 +5931,15 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -5984,22 +5979,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6025,13 +6020,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121535633</t>
+          <t>https://artportalen.se/Sighting/118197285</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130845229</v>
+        <v>121535633</v>
       </c>
       <c r="B47" t="n">
         <v>56522</v>
@@ -6070,17 +6065,17 @@
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>avlägg, Jmt</t>
+          <t>45an, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>525477</v>
+        <v>525458</v>
       </c>
       <c r="R47" t="n">
-        <v>7074694</v>
+        <v>7074700</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6104,12 +6099,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6124,44 +6129,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Nora Dahlström, Stefan Prenker</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130845229</t>
+          <t>https://artportalen.se/Sighting/121535633</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135071023</v>
+        <v>130845229</v>
       </c>
       <c r="B48" t="n">
-        <v>58844</v>
+        <v>56522</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>208249</v>
+        <v>206004</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -6169,15 +6174,14 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6215,12 +6219,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6229,7 +6233,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6247,13 +6250,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135071023</t>
+          <t>https://artportalen.se/Sighting/130845229</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135234743</v>
+        <v>135071023</v>
       </c>
       <c r="B49" t="n">
         <v>58844</v>
@@ -6283,31 +6286,27 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>45an, Jmt</t>
+          <t>avlägg, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>525458</v>
+        <v>525477</v>
       </c>
       <c r="R49" t="n">
-        <v>7074700</v>
+        <v>7074694</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6331,12 +6330,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6352,27 +6351,27 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström, Stefan Prenker</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135234743</t>
+          <t>https://artportalen.se/Sighting/135071023</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134600253</v>
+        <v>135234743</v>
       </c>
       <c r="B50" t="n">
-        <v>108205</v>
+        <v>58844</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6380,45 +6379,50 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220083</v>
+        <v>208249</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>brudborste, Jmt</t>
+          <t>45an, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>525446</v>
+        <v>525458</v>
       </c>
       <c r="R50" t="n">
-        <v>7074703</v>
+        <v>7074700</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6442,12 +6446,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6463,16 +6467,127 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Nora Dahlström, Stefan Prenker</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135234743</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>134600253</v>
+      </c>
+      <c r="B51" t="n">
+        <v>108205</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>brudborste, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>525446</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7074703</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Nora Dahlström</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Nora Dahlström, Stefan Prenker</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134600253</t>
         </is>
@@ -6529,6 +6644,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -5552,7 +5552,7 @@
         <v>135545845</v>
       </c>
       <c r="B43" t="n">
-        <v>43319</v>
+        <v>43321</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -2107,7 +2107,7 @@
         <v>136036391</v>
       </c>
       <c r="B14" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -2107,7 +2107,7 @@
         <v>136036391</v>
       </c>
       <c r="B14" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -2107,7 +2107,7 @@
         <v>136036391</v>
       </c>
       <c r="B14" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ51"/>
+  <dimension ref="A1:AZ52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2107,7 +2107,7 @@
         <v>136036391</v>
       </c>
       <c r="B14" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -4963,60 +4963,60 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129090663</v>
+        <v>136378876</v>
       </c>
       <c r="B38" t="n">
-        <v>58082</v>
+        <v>58097</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103035</v>
+        <v>103031</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>avlägg, Jmt</t>
+          <t>stig, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>525477</v>
+        <v>525548</v>
       </c>
       <c r="R38" t="n">
-        <v>7074694</v>
+        <v>7074670</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5040,12 +5040,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5071,43 +5071,43 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129090663</t>
+          <t>https://artportalen.se/Sighting/136378876</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132177647</v>
+        <v>129090663</v>
       </c>
       <c r="B39" t="n">
-        <v>58624</v>
+        <v>58082</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103042</v>
+        <v>103035</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Corvus corone</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -5120,17 +5120,17 @@
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>45an, Jmt</t>
+          <t>avlägg, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>525458</v>
+        <v>525477</v>
       </c>
       <c r="R39" t="n">
-        <v>7074700</v>
+        <v>7074694</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5154,22 +5154,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5184,44 +5174,44 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Stefan Prenker, Nora Dahlström</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132177647</t>
+          <t>https://artportalen.se/Sighting/129090663</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133167590</v>
+        <v>132177647</v>
       </c>
       <c r="B40" t="n">
-        <v>58658</v>
+        <v>58624</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103044</v>
+        <v>103042</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5231,27 +5221,27 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>vid stigen, Jmt</t>
+          <t>45an, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>525553</v>
+        <v>525458</v>
       </c>
       <c r="R40" t="n">
-        <v>7074694</v>
+        <v>7074700</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5278,22 +5268,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5319,33 +5309,33 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133167590</t>
+          <t>https://artportalen.se/Sighting/132177647</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128105819</v>
+        <v>133167590</v>
       </c>
       <c r="B41" t="n">
-        <v>43258</v>
+        <v>58658</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>201129</v>
+        <v>103044</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitfläckig guldvinge</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycaena virgaureae</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5355,27 +5345,30 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>avlägg, Jmt</t>
+          <t>vid stigen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>525477</v>
+        <v>525553</v>
       </c>
       <c r="R41" t="n">
         <v>7074694</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5399,12 +5392,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5413,56 +5416,55 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Nora Dahlström, Stefan Prenker</t>
+          <t>Stefan Prenker, Nora Dahlström</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128105819</t>
+          <t>https://artportalen.se/Sighting/133167590</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135071522</v>
+        <v>128105819</v>
       </c>
       <c r="B42" t="n">
-        <v>43319</v>
+        <v>43258</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>201146</v>
+        <v>201129</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Silverblåvinge</t>
+          <t>Vitfläckig guldvinge</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Polyommatus amandus</t>
+          <t>Lycaena virgaureae</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schneider, 1792)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5511,12 +5513,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5543,16 +5545,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135071522</t>
+          <t>https://artportalen.se/Sighting/128105819</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135545845</v>
+        <v>135071522</v>
       </c>
       <c r="B43" t="n">
-        <v>43321</v>
+        <v>43319</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5585,25 +5587,21 @@
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>t, Jmt</t>
+          <t>avlägg, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
         <v>525477</v>
       </c>
       <c r="R43" t="n">
-        <v>7074713</v>
+        <v>7074694</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5627,12 +5625,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5648,77 +5646,78 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström, Stefan Prenker</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135545845</t>
+          <t>https://artportalen.se/Sighting/135071522</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>114532044</v>
+        <v>135545845</v>
       </c>
       <c r="B44" t="n">
-        <v>58085</v>
+        <v>43321</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>205976</v>
+        <v>201146</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Silverblåvinge</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Polyommatus amandus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schneider, 1792)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>vid stigen, Jmt</t>
+          <t>t, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>525553</v>
+        <v>525477</v>
       </c>
       <c r="R44" t="n">
-        <v>7074694</v>
+        <v>7074713</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5742,12 +5741,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5756,6 +5755,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5773,13 +5773,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114532044</t>
+          <t>https://artportalen.se/Sighting/135545845</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117243737</v>
+        <v>114532044</v>
       </c>
       <c r="B45" t="n">
         <v>58085</v>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -5822,17 +5822,17 @@
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>pölen, Jmt</t>
+          <t>vid stigen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>525444</v>
+        <v>525553</v>
       </c>
       <c r="R45" t="n">
-        <v>7074699</v>
+        <v>7074694</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5856,22 +5856,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5886,24 +5876,24 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117243737</t>
+          <t>https://artportalen.se/Sighting/114532044</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118197285</v>
+        <v>117243737</v>
       </c>
       <c r="B46" t="n">
         <v>58085</v>
@@ -5936,6 +5926,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
@@ -5945,17 +5936,17 @@
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>45an, Jmt</t>
+          <t>pölen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>525458</v>
+        <v>525444</v>
       </c>
       <c r="R46" t="n">
-        <v>7074700</v>
+        <v>7074699</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5979,22 +5970,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6009,44 +6000,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118197285</t>
+          <t>https://artportalen.se/Sighting/117243737</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121535633</v>
+        <v>118197285</v>
       </c>
       <c r="B47" t="n">
-        <v>56522</v>
+        <v>58085</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>206004</v>
+        <v>205976</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -6054,12 +6045,15 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -6099,22 +6093,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6140,13 +6134,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121535633</t>
+          <t>https://artportalen.se/Sighting/118197285</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130845229</v>
+        <v>121535633</v>
       </c>
       <c r="B48" t="n">
         <v>56522</v>
@@ -6185,17 +6179,17 @@
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>avlägg, Jmt</t>
+          <t>45an, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>525477</v>
+        <v>525458</v>
       </c>
       <c r="R48" t="n">
-        <v>7074694</v>
+        <v>7074700</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6219,12 +6213,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6239,44 +6243,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Nora Dahlström, Stefan Prenker</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130845229</t>
+          <t>https://artportalen.se/Sighting/121535633</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135071023</v>
+        <v>130845229</v>
       </c>
       <c r="B49" t="n">
-        <v>58844</v>
+        <v>56522</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>208249</v>
+        <v>206004</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -6284,15 +6288,14 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6330,12 +6333,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6344,7 +6347,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6362,13 +6364,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135071023</t>
+          <t>https://artportalen.se/Sighting/130845229</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135234743</v>
+        <v>135071023</v>
       </c>
       <c r="B50" t="n">
         <v>58844</v>
@@ -6398,31 +6400,27 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>45an, Jmt</t>
+          <t>avlägg, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>525458</v>
+        <v>525477</v>
       </c>
       <c r="R50" t="n">
-        <v>7074700</v>
+        <v>7074694</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6446,12 +6444,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6467,27 +6465,27 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström, Stefan Prenker</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135234743</t>
+          <t>https://artportalen.se/Sighting/135071023</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134600253</v>
+        <v>135234743</v>
       </c>
       <c r="B51" t="n">
-        <v>108205</v>
+        <v>58844</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6495,45 +6493,50 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220083</v>
+        <v>208249</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>brudborste, Jmt</t>
+          <t>45an, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>525446</v>
+        <v>525458</v>
       </c>
       <c r="R51" t="n">
-        <v>7074703</v>
+        <v>7074700</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6557,12 +6560,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6578,16 +6581,127 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Nora Dahlström, Stefan Prenker</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135234743</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>134600253</v>
+      </c>
+      <c r="B52" t="n">
+        <v>108205</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>brudborste, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>525446</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7074703</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Nora Dahlström</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Nora Dahlström, Stefan Prenker</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134600253</t>
         </is>
@@ -6645,6 +6759,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -2107,7 +2107,7 @@
         <v>136036391</v>
       </c>
       <c r="B14" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>136378876</v>
       </c>
       <c r="B38" t="n">
-        <v>58097</v>
+        <v>58110</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ52"/>
+  <dimension ref="A1:AZ53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3545,10 +3545,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>116710205</v>
+        <v>136556155</v>
       </c>
       <c r="B26" t="n">
-        <v>58388</v>
+        <v>58446</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3556,49 +3556,49 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103001</v>
+        <v>102999</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>45an, Jmt</t>
+          <t>avlägg, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>525458</v>
+        <v>525477</v>
       </c>
       <c r="R26" t="n">
-        <v>7074700</v>
+        <v>7074694</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3622,22 +3622,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3652,61 +3642,61 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström, Stefan Prenker</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116710205</t>
+          <t>https://artportalen.se/Sighting/136556155</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126659326</v>
+        <v>116710205</v>
       </c>
       <c r="B27" t="n">
-        <v>58286</v>
+        <v>58388</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103008</v>
+        <v>103001</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3746,12 +3736,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2024-05-08</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2024-05-08</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3771,22 +3771,22 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Stefan Prenker, Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126659326</t>
+          <t>https://artportalen.se/Sighting/116710205</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134208274</v>
+        <v>126659326</v>
       </c>
       <c r="B28" t="n">
-        <v>58349</v>
+        <v>58286</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3794,16 +3794,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103015</v>
+        <v>103008</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3820,7 +3820,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3860,12 +3860,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2025-07-13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2025-07-13</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3891,13 +3891,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134208274</t>
+          <t>https://artportalen.se/Sighting/126659326</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134456500</v>
+        <v>134208274</v>
       </c>
       <c r="B29" t="n">
         <v>58349</v>
@@ -3934,20 +3934,20 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>vid stigen, Jmt</t>
+          <t>45an, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>525553</v>
+        <v>525458</v>
       </c>
       <c r="R29" t="n">
-        <v>7074694</v>
+        <v>7074700</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3974,22 +3974,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4015,16 +4005,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134456500</t>
+          <t>https://artportalen.se/Sighting/134208274</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117816937</v>
+        <v>134456500</v>
       </c>
       <c r="B30" t="n">
-        <v>58439</v>
+        <v>58349</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4032,21 +4022,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -4055,27 +4045,23 @@
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>45an, Jmt</t>
+          <t>vid stigen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>525458</v>
+        <v>525553</v>
       </c>
       <c r="R30" t="n">
-        <v>7074700</v>
+        <v>7074694</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4102,22 +4088,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4137,44 +4123,44 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Stefan Prenker, Nora Dahlström</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117816937</t>
+          <t>https://artportalen.se/Sighting/134456500</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>110849212</v>
+        <v>117816937</v>
       </c>
       <c r="B31" t="n">
-        <v>58114</v>
+        <v>58439</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>103018</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4183,23 +4169,27 @@
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>vid stigen, Jmt</t>
+          <t>45an, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>525553</v>
+        <v>525458</v>
       </c>
       <c r="R31" t="n">
-        <v>7074694</v>
+        <v>7074700</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4226,22 +4216,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-07-15</t>
+          <t>2024-06-16</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-07-15</t>
+          <t>2024-06-16</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4267,13 +4257,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110849212</t>
+          <t>https://artportalen.se/Sighting/117816937</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119104405</v>
+        <v>110849212</v>
       </c>
       <c r="B32" t="n">
         <v>58114</v>
@@ -4303,27 +4293,27 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>45an, Jmt</t>
+          <t>vid stigen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>525458</v>
+        <v>525553</v>
       </c>
       <c r="R32" t="n">
-        <v>7074700</v>
+        <v>7074694</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4350,12 +4340,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2023-07-15</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2023-07-15</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4381,13 +4381,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119104405</t>
+          <t>https://artportalen.se/Sighting/110849212</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119389819</v>
+        <v>119104405</v>
       </c>
       <c r="B33" t="n">
         <v>58114</v>
@@ -4417,7 +4417,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -4430,17 +4430,17 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>avlägg, Jmt</t>
+          <t>45an, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>525477</v>
+        <v>525458</v>
       </c>
       <c r="R33" t="n">
-        <v>7074694</v>
+        <v>7074700</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4464,12 +4464,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4484,24 +4484,24 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119389819</t>
+          <t>https://artportalen.se/Sighting/119104405</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129090796</v>
+        <v>119389819</v>
       </c>
       <c r="B34" t="n">
         <v>58114</v>
@@ -4529,25 +4529,29 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>bnm, Jmt</t>
+          <t>avlägg, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>525550</v>
+        <v>525477</v>
       </c>
       <c r="R34" t="n">
-        <v>7074647</v>
+        <v>7074694</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4574,12 +4578,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4605,16 +4609,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129090796</t>
+          <t>https://artportalen.se/Sighting/119389819</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135235591</v>
+        <v>129090796</v>
       </c>
       <c r="B35" t="n">
-        <v>58141</v>
+        <v>58114</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4639,11 +4643,7 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
@@ -4654,14 +4654,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>kj, Jmt</t>
+          <t>bnm, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>525528</v>
+        <v>525550</v>
       </c>
       <c r="R35" t="n">
-        <v>7074639</v>
+        <v>7074647</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4688,12 +4688,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4713,22 +4713,22 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Nora Dahlström, Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135235591</t>
+          <t>https://artportalen.se/Sighting/129090796</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>115275704</v>
+        <v>135235591</v>
       </c>
       <c r="B36" t="n">
-        <v>58057</v>
+        <v>58141</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4736,49 +4736,49 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>vid stigen, Jmt</t>
+          <t>kj, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>525553</v>
+        <v>525528</v>
       </c>
       <c r="R36" t="n">
-        <v>7074694</v>
+        <v>7074639</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4802,22 +4802,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4832,24 +4822,24 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström, Stefan Prenker</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115275704</t>
+          <t>https://artportalen.se/Sighting/135235591</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129540274</v>
+        <v>115275704</v>
       </c>
       <c r="B37" t="n">
         <v>58057</v>
@@ -4886,20 +4876,20 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>45an, Jmt</t>
+          <t>vid stigen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>525458</v>
+        <v>525553</v>
       </c>
       <c r="R37" t="n">
-        <v>7074700</v>
+        <v>7074694</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4926,12 +4916,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2024-03-19</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2024-03-19</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4951,22 +4951,22 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Stefan Prenker, Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129540274</t>
+          <t>https://artportalen.se/Sighting/115275704</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>136378876</v>
+        <v>129540274</v>
       </c>
       <c r="B38" t="n">
-        <v>58110</v>
+        <v>58057</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4993,30 +4993,30 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>stig, Jmt</t>
+          <t>45an, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>525548</v>
+        <v>525458</v>
       </c>
       <c r="R38" t="n">
-        <v>7074670</v>
+        <v>7074700</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5040,12 +5040,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5060,77 +5060,77 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker, Nora Dahlström</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136378876</t>
+          <t>https://artportalen.se/Sighting/129540274</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129090663</v>
+        <v>136378876</v>
       </c>
       <c r="B39" t="n">
-        <v>58082</v>
+        <v>58110</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103035</v>
+        <v>103031</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>avlägg, Jmt</t>
+          <t>stig, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>525477</v>
+        <v>525548</v>
       </c>
       <c r="R39" t="n">
-        <v>7074694</v>
+        <v>7074670</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5154,12 +5154,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5185,43 +5185,43 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129090663</t>
+          <t>https://artportalen.se/Sighting/136378876</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132177647</v>
+        <v>129090663</v>
       </c>
       <c r="B40" t="n">
-        <v>58624</v>
+        <v>58082</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103042</v>
+        <v>103035</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Corvus corone</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -5234,17 +5234,17 @@
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>45an, Jmt</t>
+          <t>avlägg, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>525458</v>
+        <v>525477</v>
       </c>
       <c r="R40" t="n">
-        <v>7074700</v>
+        <v>7074694</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5268,22 +5268,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5298,44 +5288,44 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Stefan Prenker, Nora Dahlström</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132177647</t>
+          <t>https://artportalen.se/Sighting/129090663</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133167590</v>
+        <v>132177647</v>
       </c>
       <c r="B41" t="n">
-        <v>58658</v>
+        <v>58624</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103044</v>
+        <v>103042</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5345,27 +5335,27 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>vid stigen, Jmt</t>
+          <t>45an, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>525553</v>
+        <v>525458</v>
       </c>
       <c r="R41" t="n">
-        <v>7074694</v>
+        <v>7074700</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5392,22 +5382,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5433,33 +5423,33 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133167590</t>
+          <t>https://artportalen.se/Sighting/132177647</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128105819</v>
+        <v>133167590</v>
       </c>
       <c r="B42" t="n">
-        <v>43258</v>
+        <v>58658</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>201129</v>
+        <v>103044</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitfläckig guldvinge</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycaena virgaureae</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5469,27 +5459,30 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>avlägg, Jmt</t>
+          <t>vid stigen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>525477</v>
+        <v>525553</v>
       </c>
       <c r="R42" t="n">
         <v>7074694</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5513,12 +5506,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5527,56 +5530,55 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Nora Dahlström, Stefan Prenker</t>
+          <t>Stefan Prenker, Nora Dahlström</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128105819</t>
+          <t>https://artportalen.se/Sighting/133167590</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135071522</v>
+        <v>128105819</v>
       </c>
       <c r="B43" t="n">
-        <v>43319</v>
+        <v>43258</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>201146</v>
+        <v>201129</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Silverblåvinge</t>
+          <t>Vitfläckig guldvinge</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Polyommatus amandus</t>
+          <t>Lycaena virgaureae</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schneider, 1792)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5625,12 +5627,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5657,16 +5659,16 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135071522</t>
+          <t>https://artportalen.se/Sighting/128105819</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135545845</v>
+        <v>135071522</v>
       </c>
       <c r="B44" t="n">
-        <v>43321</v>
+        <v>43319</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5699,25 +5701,21 @@
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>t, Jmt</t>
+          <t>avlägg, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
         <v>525477</v>
       </c>
       <c r="R44" t="n">
-        <v>7074713</v>
+        <v>7074694</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5741,12 +5739,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5762,77 +5760,78 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström, Stefan Prenker</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135545845</t>
+          <t>https://artportalen.se/Sighting/135071522</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>114532044</v>
+        <v>135545845</v>
       </c>
       <c r="B45" t="n">
-        <v>58085</v>
+        <v>43321</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>205976</v>
+        <v>201146</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Silverblåvinge</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Polyommatus amandus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schneider, 1792)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>vid stigen, Jmt</t>
+          <t>t, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>525553</v>
+        <v>525477</v>
       </c>
       <c r="R45" t="n">
-        <v>7074694</v>
+        <v>7074713</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5856,12 +5855,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5870,6 +5869,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5887,13 +5887,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114532044</t>
+          <t>https://artportalen.se/Sighting/135545845</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117243737</v>
+        <v>114532044</v>
       </c>
       <c r="B46" t="n">
         <v>58085</v>
@@ -5923,7 +5923,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -5936,17 +5936,17 @@
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>pölen, Jmt</t>
+          <t>vid stigen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>525444</v>
+        <v>525553</v>
       </c>
       <c r="R46" t="n">
-        <v>7074699</v>
+        <v>7074694</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5970,22 +5970,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6000,24 +5990,24 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117243737</t>
+          <t>https://artportalen.se/Sighting/114532044</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118197285</v>
+        <v>117243737</v>
       </c>
       <c r="B47" t="n">
         <v>58085</v>
@@ -6050,6 +6040,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
@@ -6059,17 +6050,17 @@
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>45an, Jmt</t>
+          <t>pölen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>525458</v>
+        <v>525444</v>
       </c>
       <c r="R47" t="n">
-        <v>7074700</v>
+        <v>7074699</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6093,22 +6084,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6123,44 +6114,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118197285</t>
+          <t>https://artportalen.se/Sighting/117243737</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121535633</v>
+        <v>118197285</v>
       </c>
       <c r="B48" t="n">
-        <v>56522</v>
+        <v>58085</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>206004</v>
+        <v>205976</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -6168,12 +6159,15 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -6213,22 +6207,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6254,13 +6248,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121535633</t>
+          <t>https://artportalen.se/Sighting/118197285</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130845229</v>
+        <v>121535633</v>
       </c>
       <c r="B49" t="n">
         <v>56522</v>
@@ -6299,17 +6293,17 @@
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>avlägg, Jmt</t>
+          <t>45an, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>525477</v>
+        <v>525458</v>
       </c>
       <c r="R49" t="n">
-        <v>7074694</v>
+        <v>7074700</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6333,12 +6327,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6353,44 +6357,44 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Nora Dahlström, Stefan Prenker</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130845229</t>
+          <t>https://artportalen.se/Sighting/121535633</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135071023</v>
+        <v>130845229</v>
       </c>
       <c r="B50" t="n">
-        <v>58844</v>
+        <v>56522</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>208249</v>
+        <v>206004</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -6398,15 +6402,14 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6444,12 +6447,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6458,7 +6461,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6476,13 +6478,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135071023</t>
+          <t>https://artportalen.se/Sighting/130845229</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135234743</v>
+        <v>135071023</v>
       </c>
       <c r="B51" t="n">
         <v>58844</v>
@@ -6512,31 +6514,27 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>45an, Jmt</t>
+          <t>avlägg, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>525458</v>
+        <v>525477</v>
       </c>
       <c r="R51" t="n">
-        <v>7074700</v>
+        <v>7074694</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6560,12 +6558,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6581,27 +6579,27 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Stefan Prenker</t>
+          <t>Nora Dahlström, Stefan Prenker</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135234743</t>
+          <t>https://artportalen.se/Sighting/135071023</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134600253</v>
+        <v>135234743</v>
       </c>
       <c r="B52" t="n">
-        <v>108205</v>
+        <v>58844</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6609,45 +6607,50 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220083</v>
+        <v>208249</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>brudborste, Jmt</t>
+          <t>45an, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>525446</v>
+        <v>525458</v>
       </c>
       <c r="R52" t="n">
-        <v>7074703</v>
+        <v>7074700</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6671,12 +6674,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6692,16 +6695,127 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Nora Dahlström</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Nora Dahlström, Stefan Prenker</t>
+          <t>Stefan Prenker</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135234743</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>134600253</v>
+      </c>
+      <c r="B53" t="n">
+        <v>108205</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>brudborste, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>525446</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7074703</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Nora Dahlström</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Nora Dahlström, Stefan Prenker</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134600253</t>
         </is>
@@ -6760,6 +6874,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
